--- a/src/test/resources/excel/诊断规范调查表-模版.xlsx
+++ b/src/test/resources/excel/诊断规范调查表-模版.xlsx
@@ -9,7 +9,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_USER\SLC\Code\IDEA_Project\smartGrid\src\test\resources\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E886EC-7519-4F2F-ABBD-F220FC0C6DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A136AF02-732B-4FA3-A57E-99335624FD0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="734" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1780,7 +1780,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2089" uniqueCount="950">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2087" uniqueCount="950">
   <si>
     <t>项目名称</t>
   </si>
@@ -5354,7 +5354,7 @@
     <numFmt numFmtId="177" formatCode="0000"/>
     <numFmt numFmtId="178" formatCode="00"/>
   </numFmts>
-  <fonts count="57">
+  <fonts count="55">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5731,22 +5731,6 @@
       <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
@@ -6301,7 +6285,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="357">
+  <cellXfs count="325">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7151,241 +7135,6 @@
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="9" borderId="5" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="9" borderId="5" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="9" borderId="14" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="9" borderId="6" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="9" borderId="5" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="9" borderId="5" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="9" borderId="5" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="9" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="9" borderId="6" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="9" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="8" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="9" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="5" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="5" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="5" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="5" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="5" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="5" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="5" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="8" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="8" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="8" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7435,6 +7184,136 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="9" borderId="6" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="8" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="9" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="5" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="5" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="5" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="5" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="5" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="5" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="5" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="8" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="8" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="8" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="21">
@@ -8212,9 +8091,7 @@
       <c r="H2" s="117"/>
       <c r="I2" s="112"/>
       <c r="J2" s="112"/>
-      <c r="K2" s="84" t="s">
-        <v>44</v>
-      </c>
+      <c r="K2" s="84"/>
       <c r="L2" s="112" t="s">
         <v>32</v>
       </c>
@@ -8340,9 +8217,7 @@
       <c r="H4" s="117"/>
       <c r="I4" s="112"/>
       <c r="J4" s="112"/>
-      <c r="K4" s="84" t="s">
-        <v>44</v>
-      </c>
+      <c r="K4" s="84"/>
       <c r="L4" s="112" t="s">
         <v>32</v>
       </c>
@@ -8381,3437 +8256,3404 @@
       <c r="AE4" s="73"/>
       <c r="AF4" s="73"/>
     </row>
-    <row r="5" spans="1:32" s="270" customFormat="1" ht="18" thickBot="1">
-      <c r="A5" s="270">
+    <row r="5" spans="1:32" ht="18" thickBot="1">
+      <c r="A5" s="43">
         <v>4</v>
       </c>
-      <c r="B5" s="271">
-        <v>1</v>
-      </c>
-      <c r="C5" s="271" t="s">
+      <c r="B5" s="112">
+        <v>1</v>
+      </c>
+      <c r="C5" s="112" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="272" t="s">
+      <c r="D5" s="114" t="s">
         <v>848</v>
       </c>
-      <c r="E5" s="272" t="s">
+      <c r="E5" s="114" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="271">
+      <c r="F5" s="112">
         <v>16</v>
       </c>
-      <c r="G5" s="273"/>
-      <c r="H5" s="274"/>
-      <c r="I5" s="271"/>
-      <c r="J5" s="271"/>
-      <c r="K5" s="275"/>
-      <c r="L5" s="271" t="s">
+      <c r="G5" s="119"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="112"/>
+      <c r="J5" s="112"/>
+      <c r="K5" s="84"/>
+      <c r="L5" s="112" t="s">
         <v>32</v>
       </c>
-      <c r="M5" s="271"/>
-      <c r="N5" s="276"/>
-      <c r="O5" s="276"/>
-      <c r="P5" s="276"/>
-      <c r="Q5" s="276"/>
-      <c r="R5" s="276"/>
-      <c r="S5" s="276"/>
-      <c r="T5" s="277"/>
-      <c r="U5" s="271"/>
-      <c r="V5" s="278" t="s">
+      <c r="M5" s="112"/>
+      <c r="N5" s="174"/>
+      <c r="O5" s="174"/>
+      <c r="P5" s="174"/>
+      <c r="Q5" s="174"/>
+      <c r="R5" s="174"/>
+      <c r="S5" s="174"/>
+      <c r="T5" s="209"/>
+      <c r="U5" s="112"/>
+      <c r="V5" s="115" t="s">
         <v>757</v>
       </c>
-      <c r="W5" s="279" t="s">
+      <c r="W5" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="X5" s="271" t="s">
+      <c r="X5" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="Y5" s="271" t="s">
+      <c r="Y5" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="Z5" s="271" t="s">
+      <c r="Z5" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AA5" s="271" t="s">
+      <c r="AA5" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AB5" s="271" t="s">
+      <c r="AB5" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AC5" s="274"/>
-      <c r="AD5" s="272"/>
-      <c r="AE5" s="280"/>
-      <c r="AF5" s="280"/>
-    </row>
-    <row r="6" spans="1:32" s="270" customFormat="1" ht="18" thickBot="1">
-      <c r="A6" s="270">
+      <c r="AC5" s="117"/>
+      <c r="AD5" s="114"/>
+      <c r="AE5" s="73"/>
+      <c r="AF5" s="73"/>
+    </row>
+    <row r="6" spans="1:32" ht="18" thickBot="1">
+      <c r="A6" s="43">
         <v>5</v>
       </c>
-      <c r="B6" s="271">
-        <v>1</v>
-      </c>
-      <c r="C6" s="271" t="s">
+      <c r="B6" s="112">
+        <v>1</v>
+      </c>
+      <c r="C6" s="112" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="272" t="s">
+      <c r="D6" s="114" t="s">
         <v>849</v>
       </c>
-      <c r="E6" s="272" t="s">
+      <c r="E6" s="114" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="271">
+      <c r="F6" s="112">
         <v>16</v>
       </c>
-      <c r="G6" s="273"/>
-      <c r="H6" s="274"/>
-      <c r="I6" s="271"/>
-      <c r="J6" s="271"/>
-      <c r="K6" s="275"/>
-      <c r="L6" s="271" t="s">
+      <c r="G6" s="119"/>
+      <c r="H6" s="117"/>
+      <c r="I6" s="112"/>
+      <c r="J6" s="112"/>
+      <c r="K6" s="84"/>
+      <c r="L6" s="112" t="s">
         <v>32</v>
       </c>
-      <c r="M6" s="271"/>
-      <c r="N6" s="276"/>
-      <c r="O6" s="276"/>
-      <c r="P6" s="276"/>
-      <c r="Q6" s="276"/>
-      <c r="R6" s="276"/>
-      <c r="S6" s="276"/>
-      <c r="T6" s="277"/>
-      <c r="U6" s="271"/>
-      <c r="V6" s="278" t="s">
+      <c r="M6" s="112"/>
+      <c r="N6" s="174"/>
+      <c r="O6" s="174"/>
+      <c r="P6" s="174"/>
+      <c r="Q6" s="174"/>
+      <c r="R6" s="174"/>
+      <c r="S6" s="174"/>
+      <c r="T6" s="209"/>
+      <c r="U6" s="112"/>
+      <c r="V6" s="115" t="s">
         <v>757</v>
       </c>
-      <c r="W6" s="279" t="s">
+      <c r="W6" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="X6" s="271" t="s">
+      <c r="X6" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="Y6" s="271" t="s">
+      <c r="Y6" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="Z6" s="271" t="s">
+      <c r="Z6" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AA6" s="271" t="s">
+      <c r="AA6" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AB6" s="271" t="s">
+      <c r="AB6" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AC6" s="274"/>
-      <c r="AD6" s="272"/>
-      <c r="AE6" s="280"/>
-      <c r="AF6" s="280"/>
-    </row>
-    <row r="7" spans="1:32" s="270" customFormat="1" ht="18" thickBot="1">
-      <c r="A7" s="270">
+      <c r="AC6" s="117"/>
+      <c r="AD6" s="114"/>
+      <c r="AE6" s="73"/>
+      <c r="AF6" s="73"/>
+    </row>
+    <row r="7" spans="1:32" ht="18" thickBot="1">
+      <c r="A7" s="43">
         <v>6</v>
       </c>
-      <c r="B7" s="271">
-        <v>1</v>
-      </c>
-      <c r="C7" s="271" t="s">
+      <c r="B7" s="112">
+        <v>1</v>
+      </c>
+      <c r="C7" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="272" t="s">
+      <c r="D7" s="114" t="s">
         <v>936</v>
       </c>
-      <c r="E7" s="272" t="s">
+      <c r="E7" s="114" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="271">
+      <c r="F7" s="112">
         <v>13</v>
       </c>
-      <c r="G7" s="273"/>
-      <c r="H7" s="274"/>
-      <c r="I7" s="271"/>
-      <c r="J7" s="271"/>
-      <c r="K7" s="275"/>
-      <c r="L7" s="271" t="s">
+      <c r="G7" s="119"/>
+      <c r="H7" s="117"/>
+      <c r="I7" s="112"/>
+      <c r="J7" s="112"/>
+      <c r="K7" s="84"/>
+      <c r="L7" s="112" t="s">
         <v>32</v>
       </c>
-      <c r="M7" s="271"/>
-      <c r="N7" s="276"/>
-      <c r="O7" s="276"/>
-      <c r="P7" s="276"/>
-      <c r="Q7" s="276"/>
-      <c r="R7" s="276"/>
-      <c r="S7" s="276"/>
-      <c r="T7" s="277"/>
-      <c r="U7" s="271"/>
-      <c r="V7" s="278" t="s">
+      <c r="M7" s="112"/>
+      <c r="N7" s="174"/>
+      <c r="O7" s="174"/>
+      <c r="P7" s="174"/>
+      <c r="Q7" s="174"/>
+      <c r="R7" s="174"/>
+      <c r="S7" s="174"/>
+      <c r="T7" s="209"/>
+      <c r="U7" s="112"/>
+      <c r="V7" s="115" t="s">
         <v>757</v>
       </c>
-      <c r="W7" s="279" t="s">
+      <c r="W7" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="X7" s="271" t="s">
+      <c r="X7" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="Y7" s="271" t="s">
+      <c r="Y7" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="Z7" s="271" t="s">
+      <c r="Z7" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AA7" s="271" t="s">
+      <c r="AA7" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AB7" s="271" t="s">
+      <c r="AB7" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AC7" s="274"/>
-      <c r="AD7" s="272" t="s">
+      <c r="AC7" s="117"/>
+      <c r="AD7" s="114" t="s">
         <v>50</v>
       </c>
-      <c r="AE7" s="280"/>
-      <c r="AF7" s="280"/>
-    </row>
-    <row r="8" spans="1:32" s="270" customFormat="1" ht="18" thickBot="1">
-      <c r="A8" s="270">
+      <c r="AE7" s="73"/>
+      <c r="AF7" s="73"/>
+    </row>
+    <row r="8" spans="1:32" ht="18" thickBot="1">
+      <c r="A8" s="43">
         <v>7</v>
       </c>
-      <c r="B8" s="271">
-        <v>1</v>
-      </c>
-      <c r="C8" s="271" t="s">
+      <c r="B8" s="112">
+        <v>1</v>
+      </c>
+      <c r="C8" s="112" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="272" t="s">
+      <c r="D8" s="114" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="272" t="s">
+      <c r="E8" s="114" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="271">
+      <c r="F8" s="112">
         <v>24</v>
       </c>
-      <c r="G8" s="273"/>
-      <c r="H8" s="274"/>
-      <c r="I8" s="271"/>
-      <c r="J8" s="271"/>
-      <c r="K8" s="275"/>
-      <c r="L8" s="271" t="s">
+      <c r="G8" s="119"/>
+      <c r="H8" s="117"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="112"/>
+      <c r="K8" s="84"/>
+      <c r="L8" s="112" t="s">
         <v>32</v>
       </c>
-      <c r="M8" s="271"/>
-      <c r="N8" s="276"/>
-      <c r="O8" s="276"/>
-      <c r="P8" s="276"/>
-      <c r="Q8" s="276"/>
-      <c r="R8" s="276"/>
-      <c r="S8" s="276"/>
-      <c r="T8" s="277"/>
-      <c r="U8" s="271"/>
-      <c r="V8" s="278" t="s">
+      <c r="M8" s="112"/>
+      <c r="N8" s="174"/>
+      <c r="O8" s="174"/>
+      <c r="P8" s="174"/>
+      <c r="Q8" s="174"/>
+      <c r="R8" s="174"/>
+      <c r="S8" s="174"/>
+      <c r="T8" s="209"/>
+      <c r="U8" s="112"/>
+      <c r="V8" s="115" t="s">
         <v>757</v>
       </c>
-      <c r="W8" s="279" t="s">
+      <c r="W8" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="X8" s="271" t="s">
+      <c r="X8" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="Y8" s="271" t="s">
+      <c r="Y8" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="Z8" s="271" t="s">
+      <c r="Z8" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AA8" s="271" t="s">
+      <c r="AA8" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AB8" s="271" t="s">
+      <c r="AB8" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AC8" s="274"/>
-      <c r="AD8" s="272"/>
-      <c r="AE8" s="280"/>
-      <c r="AF8" s="280"/>
-    </row>
-    <row r="9" spans="1:32" s="270" customFormat="1" ht="18" thickBot="1">
-      <c r="A9" s="270">
+      <c r="AC8" s="117"/>
+      <c r="AD8" s="114"/>
+      <c r="AE8" s="73"/>
+      <c r="AF8" s="73"/>
+    </row>
+    <row r="9" spans="1:32" ht="18" thickBot="1">
+      <c r="A9" s="43">
         <v>8</v>
       </c>
-      <c r="B9" s="271">
-        <v>1</v>
-      </c>
-      <c r="C9" s="271" t="s">
+      <c r="B9" s="112">
+        <v>1</v>
+      </c>
+      <c r="C9" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="272" t="s">
+      <c r="D9" s="114" t="s">
         <v>937</v>
       </c>
-      <c r="E9" s="272" t="s">
+      <c r="E9" s="114" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="271">
+      <c r="F9" s="112">
         <v>4</v>
       </c>
-      <c r="G9" s="273"/>
-      <c r="H9" s="274"/>
-      <c r="I9" s="271"/>
-      <c r="J9" s="271"/>
-      <c r="K9" s="275"/>
-      <c r="L9" s="271" t="s">
+      <c r="G9" s="119"/>
+      <c r="H9" s="117"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="112"/>
+      <c r="K9" s="84"/>
+      <c r="L9" s="112" t="s">
         <v>34</v>
       </c>
-      <c r="M9" s="271"/>
-      <c r="N9" s="276"/>
-      <c r="O9" s="276"/>
-      <c r="P9" s="276"/>
-      <c r="Q9" s="276"/>
-      <c r="R9" s="276"/>
-      <c r="S9" s="276"/>
-      <c r="T9" s="277"/>
-      <c r="U9" s="271"/>
-      <c r="V9" s="278" t="s">
+      <c r="M9" s="112"/>
+      <c r="N9" s="174"/>
+      <c r="O9" s="174"/>
+      <c r="P9" s="174"/>
+      <c r="Q9" s="174"/>
+      <c r="R9" s="174"/>
+      <c r="S9" s="174"/>
+      <c r="T9" s="209"/>
+      <c r="U9" s="112"/>
+      <c r="V9" s="115" t="s">
         <v>753</v>
       </c>
-      <c r="W9" s="279" t="s">
+      <c r="W9" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="X9" s="271" t="s">
+      <c r="X9" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="Y9" s="271" t="s">
+      <c r="Y9" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="Z9" s="271" t="s">
+      <c r="Z9" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AA9" s="271" t="s">
+      <c r="AA9" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB9" s="271" t="s">
+      <c r="AB9" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AC9" s="281"/>
-      <c r="AD9" s="271"/>
-      <c r="AE9" s="280"/>
-      <c r="AF9" s="280"/>
-    </row>
-    <row r="10" spans="1:32" s="270" customFormat="1" ht="18" thickBot="1">
-      <c r="A10" s="270">
+      <c r="AC9" s="286"/>
+      <c r="AD9" s="112"/>
+      <c r="AE9" s="73"/>
+      <c r="AF9" s="73"/>
+    </row>
+    <row r="10" spans="1:32" ht="18" thickBot="1">
+      <c r="A10" s="43">
         <v>9</v>
       </c>
-      <c r="B10" s="271">
-        <v>1</v>
-      </c>
-      <c r="C10" s="271" t="s">
+      <c r="B10" s="112">
+        <v>1</v>
+      </c>
+      <c r="C10" s="112" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="272" t="s">
+      <c r="D10" s="114" t="s">
         <v>938</v>
       </c>
-      <c r="E10" s="272" t="s">
+      <c r="E10" s="114" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="271">
+      <c r="F10" s="112">
         <v>10</v>
       </c>
-      <c r="G10" s="273"/>
-      <c r="H10" s="274"/>
-      <c r="I10" s="271"/>
-      <c r="J10" s="271"/>
-      <c r="K10" s="275"/>
-      <c r="L10" s="271" t="s">
+      <c r="G10" s="119"/>
+      <c r="H10" s="117"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="112"/>
+      <c r="K10" s="84"/>
+      <c r="L10" s="112" t="s">
         <v>32</v>
       </c>
-      <c r="M10" s="271"/>
-      <c r="N10" s="276"/>
-      <c r="O10" s="276"/>
-      <c r="P10" s="276"/>
-      <c r="Q10" s="276"/>
-      <c r="R10" s="276"/>
-      <c r="S10" s="276"/>
-      <c r="T10" s="277"/>
-      <c r="U10" s="271"/>
-      <c r="V10" s="278" t="s">
+      <c r="M10" s="112"/>
+      <c r="N10" s="174"/>
+      <c r="O10" s="174"/>
+      <c r="P10" s="174"/>
+      <c r="Q10" s="174"/>
+      <c r="R10" s="174"/>
+      <c r="S10" s="174"/>
+      <c r="T10" s="209"/>
+      <c r="U10" s="112"/>
+      <c r="V10" s="115" t="s">
         <v>753</v>
       </c>
-      <c r="W10" s="279" t="s">
+      <c r="W10" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="X10" s="271" t="s">
+      <c r="X10" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="Y10" s="271" t="s">
+      <c r="Y10" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="Z10" s="271" t="s">
+      <c r="Z10" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AA10" s="271" t="s">
+      <c r="AA10" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB10" s="271" t="s">
+      <c r="AB10" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AC10" s="281"/>
-      <c r="AD10" s="271"/>
-      <c r="AE10" s="280"/>
-      <c r="AF10" s="280"/>
-    </row>
-    <row r="11" spans="1:32" s="270" customFormat="1" ht="18" thickBot="1">
-      <c r="A11" s="270">
+      <c r="AC10" s="286"/>
+      <c r="AD10" s="112"/>
+      <c r="AE10" s="73"/>
+      <c r="AF10" s="73"/>
+    </row>
+    <row r="11" spans="1:32" ht="18" thickBot="1">
+      <c r="A11" s="43">
         <v>10</v>
       </c>
-      <c r="B11" s="271">
-        <v>1</v>
-      </c>
-      <c r="C11" s="271" t="s">
+      <c r="B11" s="112">
+        <v>1</v>
+      </c>
+      <c r="C11" s="112" t="s">
         <v>789</v>
       </c>
-      <c r="D11" s="272" t="s">
+      <c r="D11" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="E11" s="272" t="s">
+      <c r="E11" s="114" t="s">
         <v>57</v>
       </c>
-      <c r="F11" s="282">
+      <c r="F11" s="113">
         <v>8</v>
       </c>
-      <c r="G11" s="273"/>
-      <c r="H11" s="274"/>
-      <c r="I11" s="271"/>
-      <c r="J11" s="271"/>
-      <c r="K11" s="275"/>
-      <c r="L11" s="271" t="s">
+      <c r="G11" s="119"/>
+      <c r="H11" s="117"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="112"/>
+      <c r="K11" s="84"/>
+      <c r="L11" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="M11" s="271"/>
-      <c r="N11" s="276"/>
-      <c r="O11" s="276"/>
-      <c r="P11" s="276"/>
-      <c r="Q11" s="276"/>
-      <c r="R11" s="276"/>
-      <c r="S11" s="276"/>
-      <c r="T11" s="277"/>
-      <c r="U11" s="271"/>
-      <c r="V11" s="278" t="s">
+      <c r="M11" s="112"/>
+      <c r="N11" s="174"/>
+      <c r="O11" s="174"/>
+      <c r="P11" s="174"/>
+      <c r="Q11" s="174"/>
+      <c r="R11" s="174"/>
+      <c r="S11" s="174"/>
+      <c r="T11" s="209"/>
+      <c r="U11" s="112"/>
+      <c r="V11" s="115" t="s">
         <v>753</v>
       </c>
-      <c r="W11" s="279" t="s">
+      <c r="W11" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="X11" s="271" t="s">
+      <c r="X11" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="Y11" s="271" t="s">
+      <c r="Y11" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="Z11" s="271" t="s">
+      <c r="Z11" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AA11" s="271" t="s">
+      <c r="AA11" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB11" s="271" t="s">
+      <c r="AB11" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AC11" s="281"/>
-      <c r="AD11" s="271"/>
-      <c r="AE11" s="280"/>
-      <c r="AF11" s="280"/>
-    </row>
-    <row r="12" spans="1:32" s="270" customFormat="1" ht="34.5">
-      <c r="A12" s="270">
+      <c r="AC11" s="286"/>
+      <c r="AD11" s="112"/>
+      <c r="AE11" s="73"/>
+      <c r="AF11" s="73"/>
+    </row>
+    <row r="12" spans="1:32" ht="34.5">
+      <c r="A12" s="43">
         <v>11</v>
       </c>
-      <c r="B12" s="270">
+      <c r="B12" s="43">
         <v>2</v>
       </c>
-      <c r="C12" s="283"/>
-      <c r="D12" s="284"/>
-      <c r="E12" s="284"/>
-      <c r="F12" s="283"/>
-      <c r="G12" s="285" t="s">
+      <c r="C12" s="287"/>
+      <c r="D12" s="175"/>
+      <c r="E12" s="175"/>
+      <c r="F12" s="287"/>
+      <c r="G12" s="120" t="s">
         <v>58</v>
       </c>
-      <c r="H12" s="286" t="s">
+      <c r="H12" s="121" t="s">
         <v>59</v>
       </c>
-      <c r="I12" s="287">
+      <c r="I12" s="288">
         <v>4</v>
       </c>
-      <c r="J12" s="287">
+      <c r="J12" s="288">
         <v>4</v>
       </c>
-      <c r="K12" s="275" t="s">
+      <c r="K12" s="84" t="s">
         <v>340</v>
       </c>
-      <c r="L12" s="287" t="s">
+      <c r="L12" s="288" t="s">
         <v>16</v>
       </c>
-      <c r="M12" s="275">
-        <v>1</v>
-      </c>
-      <c r="N12" s="286">
+      <c r="M12" s="84">
+        <v>1</v>
+      </c>
+      <c r="N12" s="121">
         <v>0</v>
       </c>
-      <c r="O12" s="286"/>
-      <c r="P12" s="286"/>
-      <c r="Q12" s="286"/>
-      <c r="R12" s="286"/>
-      <c r="S12" s="286"/>
-      <c r="T12" s="288" t="s">
+      <c r="O12" s="121"/>
+      <c r="P12" s="121"/>
+      <c r="Q12" s="121"/>
+      <c r="R12" s="121"/>
+      <c r="S12" s="121"/>
+      <c r="T12" s="33" t="s">
         <v>831</v>
       </c>
-      <c r="U12" s="275"/>
-      <c r="V12" s="289"/>
-      <c r="W12" s="290"/>
-      <c r="X12" s="291"/>
-      <c r="Y12" s="291"/>
-      <c r="Z12" s="291"/>
-      <c r="AA12" s="291"/>
-      <c r="AB12" s="291"/>
-      <c r="AC12" s="292"/>
-      <c r="AD12" s="293"/>
-      <c r="AE12" s="280" t="s">
+      <c r="U12" s="84"/>
+      <c r="V12" s="85"/>
+      <c r="W12" s="289"/>
+      <c r="X12" s="290"/>
+      <c r="Y12" s="290"/>
+      <c r="Z12" s="290"/>
+      <c r="AA12" s="290"/>
+      <c r="AB12" s="290"/>
+      <c r="AC12" s="291"/>
+      <c r="AD12" s="292"/>
+      <c r="AE12" s="73" t="s">
         <v>741</v>
       </c>
-      <c r="AF12" s="280" t="s">
+      <c r="AF12" s="73" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="13" spans="1:32" s="270" customFormat="1" ht="33.75" customHeight="1">
-      <c r="A13" s="270">
+    <row r="13" spans="1:32" ht="33.75" customHeight="1">
+      <c r="A13" s="43">
         <v>12</v>
       </c>
-      <c r="B13" s="270">
+      <c r="B13" s="43">
         <v>2</v>
       </c>
-      <c r="C13" s="283"/>
-      <c r="D13" s="284"/>
-      <c r="E13" s="284"/>
-      <c r="F13" s="283"/>
-      <c r="G13" s="286" t="s">
+      <c r="C13" s="287"/>
+      <c r="D13" s="175"/>
+      <c r="E13" s="175"/>
+      <c r="F13" s="287"/>
+      <c r="G13" s="121" t="s">
         <v>909</v>
       </c>
-      <c r="H13" s="286" t="s">
+      <c r="H13" s="121" t="s">
         <v>910</v>
       </c>
-      <c r="I13" s="287" t="s">
+      <c r="I13" s="288" t="s">
         <v>828</v>
       </c>
-      <c r="J13" s="287">
+      <c r="J13" s="288">
         <v>4</v>
       </c>
-      <c r="K13" s="275" t="s">
+      <c r="K13" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="L13" s="287" t="s">
+      <c r="L13" s="288" t="s">
         <v>16</v>
       </c>
-      <c r="M13" s="275">
-        <v>1</v>
-      </c>
-      <c r="N13" s="286">
+      <c r="M13" s="84">
+        <v>1</v>
+      </c>
+      <c r="N13" s="121">
         <v>0</v>
       </c>
-      <c r="O13" s="286"/>
-      <c r="P13" s="286"/>
-      <c r="Q13" s="286"/>
-      <c r="R13" s="286"/>
-      <c r="S13" s="286"/>
-      <c r="T13" s="288" t="s">
+      <c r="O13" s="121"/>
+      <c r="P13" s="121"/>
+      <c r="Q13" s="121"/>
+      <c r="R13" s="121"/>
+      <c r="S13" s="121"/>
+      <c r="T13" s="33" t="s">
         <v>832</v>
       </c>
-      <c r="U13" s="275"/>
-      <c r="V13" s="289"/>
-      <c r="W13" s="290"/>
-      <c r="X13" s="291"/>
-      <c r="Y13" s="291"/>
-      <c r="Z13" s="291"/>
-      <c r="AA13" s="291"/>
-      <c r="AB13" s="291"/>
-      <c r="AC13" s="292"/>
-      <c r="AD13" s="293"/>
-      <c r="AE13" s="280" t="s">
+      <c r="U13" s="84"/>
+      <c r="V13" s="85"/>
+      <c r="W13" s="289"/>
+      <c r="X13" s="290"/>
+      <c r="Y13" s="290"/>
+      <c r="Z13" s="290"/>
+      <c r="AA13" s="290"/>
+      <c r="AB13" s="290"/>
+      <c r="AC13" s="291"/>
+      <c r="AD13" s="292"/>
+      <c r="AE13" s="73" t="s">
         <v>742</v>
       </c>
-      <c r="AF13" s="280" t="s">
+      <c r="AF13" s="73" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="14" spans="1:32" s="270" customFormat="1" ht="34.5">
-      <c r="A14" s="270">
+    <row r="14" spans="1:32" ht="34.5">
+      <c r="A14" s="43">
         <v>13</v>
       </c>
-      <c r="B14" s="270">
+      <c r="B14" s="43">
         <v>2</v>
       </c>
-      <c r="C14" s="283"/>
-      <c r="D14" s="284"/>
-      <c r="E14" s="284"/>
-      <c r="F14" s="283"/>
-      <c r="G14" s="286" t="s">
+      <c r="C14" s="287"/>
+      <c r="D14" s="175"/>
+      <c r="E14" s="175"/>
+      <c r="F14" s="287"/>
+      <c r="G14" s="121" t="s">
         <v>940</v>
       </c>
-      <c r="H14" s="286" t="s">
+      <c r="H14" s="121" t="s">
         <v>60</v>
       </c>
-      <c r="I14" s="287">
+      <c r="I14" s="288">
         <v>8</v>
       </c>
-      <c r="J14" s="287">
+      <c r="J14" s="288">
         <v>8</v>
       </c>
-      <c r="K14" s="275" t="s">
+      <c r="K14" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="L14" s="287" t="s">
+      <c r="L14" s="288" t="s">
         <v>16</v>
       </c>
-      <c r="M14" s="275">
-        <v>1</v>
-      </c>
-      <c r="N14" s="286">
+      <c r="M14" s="84">
+        <v>1</v>
+      </c>
+      <c r="N14" s="121">
         <v>0</v>
       </c>
-      <c r="O14" s="286"/>
-      <c r="P14" s="286"/>
-      <c r="Q14" s="286"/>
-      <c r="R14" s="286"/>
-      <c r="S14" s="286"/>
-      <c r="T14" s="288" t="s">
+      <c r="O14" s="121"/>
+      <c r="P14" s="121"/>
+      <c r="Q14" s="121"/>
+      <c r="R14" s="121"/>
+      <c r="S14" s="121"/>
+      <c r="T14" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="U14" s="275"/>
-      <c r="V14" s="289"/>
-      <c r="W14" s="290"/>
-      <c r="X14" s="291"/>
-      <c r="Y14" s="291"/>
-      <c r="Z14" s="291"/>
-      <c r="AA14" s="291"/>
-      <c r="AB14" s="291"/>
-      <c r="AC14" s="292"/>
-      <c r="AD14" s="293"/>
-      <c r="AE14" s="280" t="s">
+      <c r="U14" s="84"/>
+      <c r="V14" s="85"/>
+      <c r="W14" s="289"/>
+      <c r="X14" s="290"/>
+      <c r="Y14" s="290"/>
+      <c r="Z14" s="290"/>
+      <c r="AA14" s="290"/>
+      <c r="AB14" s="290"/>
+      <c r="AC14" s="291"/>
+      <c r="AD14" s="292"/>
+      <c r="AE14" s="73" t="s">
         <v>828</v>
       </c>
-      <c r="AF14" s="280" t="s">
+      <c r="AF14" s="73" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="15" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A15" s="270">
+    <row r="15" spans="1:32" ht="17.25">
+      <c r="A15" s="43">
         <v>14</v>
       </c>
-      <c r="B15" s="270">
+      <c r="B15" s="43">
         <v>2</v>
       </c>
-      <c r="C15" s="283"/>
-      <c r="D15" s="284"/>
-      <c r="E15" s="284"/>
-      <c r="F15" s="283"/>
-      <c r="G15" s="294" t="s">
+      <c r="C15" s="287"/>
+      <c r="D15" s="175"/>
+      <c r="E15" s="175"/>
+      <c r="F15" s="287"/>
+      <c r="G15" s="293" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="294" t="s">
+      <c r="H15" s="293" t="s">
         <v>62</v>
       </c>
-      <c r="I15" s="287">
+      <c r="I15" s="288">
         <v>23</v>
       </c>
-      <c r="J15" s="287">
-        <v>1</v>
-      </c>
-      <c r="K15" s="275" t="s">
+      <c r="J15" s="288">
+        <v>1</v>
+      </c>
+      <c r="K15" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="L15" s="287" t="s">
+      <c r="L15" s="288" t="s">
         <v>16</v>
       </c>
-      <c r="M15" s="275">
-        <v>1</v>
-      </c>
-      <c r="N15" s="286">
+      <c r="M15" s="84">
+        <v>1</v>
+      </c>
+      <c r="N15" s="121">
         <v>0</v>
       </c>
-      <c r="O15" s="286"/>
-      <c r="P15" s="286"/>
-      <c r="Q15" s="286"/>
-      <c r="R15" s="286"/>
-      <c r="S15" s="286"/>
-      <c r="T15" s="288" t="s">
+      <c r="O15" s="121"/>
+      <c r="P15" s="121"/>
+      <c r="Q15" s="121"/>
+      <c r="R15" s="121"/>
+      <c r="S15" s="121"/>
+      <c r="T15" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="U15" s="275"/>
-      <c r="V15" s="289"/>
-      <c r="W15" s="290"/>
-      <c r="X15" s="291"/>
-      <c r="Y15" s="291"/>
-      <c r="Z15" s="291"/>
-      <c r="AA15" s="291"/>
-      <c r="AB15" s="291"/>
-      <c r="AC15" s="292"/>
-      <c r="AD15" s="293"/>
-      <c r="AE15" s="280" t="s">
+      <c r="U15" s="84"/>
+      <c r="V15" s="85"/>
+      <c r="W15" s="289"/>
+      <c r="X15" s="290"/>
+      <c r="Y15" s="290"/>
+      <c r="Z15" s="290"/>
+      <c r="AA15" s="290"/>
+      <c r="AB15" s="290"/>
+      <c r="AC15" s="291"/>
+      <c r="AD15" s="292"/>
+      <c r="AE15" s="73" t="s">
         <v>828</v>
       </c>
-      <c r="AF15" s="280" t="s">
+      <c r="AF15" s="73" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="16" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A16" s="270">
+    <row r="16" spans="1:32" ht="17.25">
+      <c r="A16" s="43">
         <v>15</v>
       </c>
-      <c r="B16" s="270">
+      <c r="B16" s="43">
         <v>2</v>
       </c>
-      <c r="C16" s="283"/>
-      <c r="D16" s="284"/>
-      <c r="E16" s="284"/>
-      <c r="F16" s="283"/>
-      <c r="G16" s="294" t="s">
+      <c r="C16" s="287"/>
+      <c r="D16" s="175"/>
+      <c r="E16" s="175"/>
+      <c r="F16" s="287"/>
+      <c r="G16" s="293" t="s">
         <v>64</v>
       </c>
-      <c r="H16" s="294" t="s">
+      <c r="H16" s="293" t="s">
         <v>64</v>
       </c>
-      <c r="I16" s="287">
+      <c r="I16" s="288">
         <v>22</v>
       </c>
-      <c r="J16" s="287">
-        <v>1</v>
-      </c>
-      <c r="K16" s="275" t="s">
+      <c r="J16" s="288">
+        <v>1</v>
+      </c>
+      <c r="K16" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="L16" s="287" t="s">
+      <c r="L16" s="288" t="s">
         <v>16</v>
       </c>
-      <c r="M16" s="275">
-        <v>1</v>
-      </c>
-      <c r="N16" s="286">
+      <c r="M16" s="84">
+        <v>1</v>
+      </c>
+      <c r="N16" s="121">
         <v>0</v>
       </c>
-      <c r="O16" s="286"/>
-      <c r="P16" s="286"/>
-      <c r="Q16" s="286"/>
-      <c r="R16" s="286"/>
-      <c r="S16" s="286"/>
-      <c r="T16" s="288" t="s">
+      <c r="O16" s="121"/>
+      <c r="P16" s="121"/>
+      <c r="Q16" s="121"/>
+      <c r="R16" s="121"/>
+      <c r="S16" s="121"/>
+      <c r="T16" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="U16" s="275"/>
-      <c r="V16" s="289"/>
-      <c r="W16" s="290"/>
-      <c r="X16" s="291"/>
-      <c r="Y16" s="291"/>
-      <c r="Z16" s="291"/>
-      <c r="AA16" s="291"/>
-      <c r="AB16" s="291"/>
-      <c r="AC16" s="292"/>
-      <c r="AD16" s="293"/>
-      <c r="AE16" s="280" t="s">
+      <c r="U16" s="84"/>
+      <c r="V16" s="85"/>
+      <c r="W16" s="289"/>
+      <c r="X16" s="290"/>
+      <c r="Y16" s="290"/>
+      <c r="Z16" s="290"/>
+      <c r="AA16" s="290"/>
+      <c r="AB16" s="290"/>
+      <c r="AC16" s="291"/>
+      <c r="AD16" s="292"/>
+      <c r="AE16" s="73" t="s">
         <v>828</v>
       </c>
-      <c r="AF16" s="280" t="s">
+      <c r="AF16" s="73" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="17" spans="1:33" s="270" customFormat="1" ht="17.25">
-      <c r="A17" s="270">
+    <row r="17" spans="1:33" ht="17.25">
+      <c r="A17" s="43">
         <v>16</v>
       </c>
-      <c r="B17" s="270">
+      <c r="B17" s="43">
         <v>2</v>
       </c>
-      <c r="C17" s="283"/>
-      <c r="D17" s="284"/>
-      <c r="E17" s="284"/>
-      <c r="F17" s="283"/>
-      <c r="G17" s="294" t="s">
+      <c r="C17" s="287"/>
+      <c r="D17" s="175"/>
+      <c r="E17" s="175"/>
+      <c r="F17" s="287"/>
+      <c r="G17" s="293" t="s">
         <v>65</v>
       </c>
-      <c r="H17" s="294" t="s">
+      <c r="H17" s="293" t="s">
         <v>65</v>
       </c>
-      <c r="I17" s="287">
+      <c r="I17" s="288">
         <v>21</v>
       </c>
-      <c r="J17" s="287">
-        <v>1</v>
-      </c>
-      <c r="K17" s="275" t="s">
+      <c r="J17" s="288">
+        <v>1</v>
+      </c>
+      <c r="K17" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="L17" s="287" t="s">
+      <c r="L17" s="288" t="s">
         <v>16</v>
       </c>
-      <c r="M17" s="275">
-        <v>1</v>
-      </c>
-      <c r="N17" s="286">
+      <c r="M17" s="84">
+        <v>1</v>
+      </c>
+      <c r="N17" s="121">
         <v>0</v>
       </c>
-      <c r="O17" s="286"/>
-      <c r="P17" s="286"/>
-      <c r="Q17" s="286"/>
-      <c r="R17" s="286"/>
-      <c r="S17" s="286"/>
-      <c r="T17" s="288" t="s">
+      <c r="O17" s="121"/>
+      <c r="P17" s="121"/>
+      <c r="Q17" s="121"/>
+      <c r="R17" s="121"/>
+      <c r="S17" s="121"/>
+      <c r="T17" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="U17" s="275"/>
-      <c r="V17" s="289"/>
-      <c r="W17" s="290"/>
-      <c r="X17" s="291"/>
-      <c r="Y17" s="291"/>
-      <c r="Z17" s="291"/>
-      <c r="AA17" s="291"/>
-      <c r="AB17" s="291"/>
-      <c r="AC17" s="292"/>
-      <c r="AD17" s="293"/>
-      <c r="AE17" s="280" t="s">
+      <c r="U17" s="84"/>
+      <c r="V17" s="85"/>
+      <c r="W17" s="289"/>
+      <c r="X17" s="290"/>
+      <c r="Y17" s="290"/>
+      <c r="Z17" s="290"/>
+      <c r="AA17" s="290"/>
+      <c r="AB17" s="290"/>
+      <c r="AC17" s="291"/>
+      <c r="AD17" s="292"/>
+      <c r="AE17" s="73" t="s">
         <v>828</v>
       </c>
-      <c r="AF17" s="280" t="s">
+      <c r="AF17" s="73" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="18" spans="1:33" s="270" customFormat="1" ht="17.25">
-      <c r="A18" s="270">
+    <row r="18" spans="1:33" ht="17.25">
+      <c r="A18" s="43">
         <v>17</v>
       </c>
-      <c r="B18" s="270">
+      <c r="B18" s="43">
         <v>2</v>
       </c>
-      <c r="C18" s="283"/>
-      <c r="D18" s="284"/>
-      <c r="E18" s="284"/>
-      <c r="F18" s="283"/>
-      <c r="G18" s="294" t="s">
+      <c r="C18" s="287"/>
+      <c r="D18" s="175"/>
+      <c r="E18" s="175"/>
+      <c r="F18" s="287"/>
+      <c r="G18" s="293" t="s">
         <v>337</v>
       </c>
-      <c r="H18" s="294" t="s">
+      <c r="H18" s="293" t="s">
         <v>66</v>
       </c>
-      <c r="I18" s="287">
+      <c r="I18" s="288">
         <v>20</v>
       </c>
-      <c r="J18" s="287">
-        <v>1</v>
-      </c>
-      <c r="K18" s="275" t="s">
+      <c r="J18" s="288">
+        <v>1</v>
+      </c>
+      <c r="K18" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="L18" s="287" t="s">
+      <c r="L18" s="288" t="s">
         <v>16</v>
       </c>
-      <c r="M18" s="275">
-        <v>1</v>
-      </c>
-      <c r="N18" s="286">
+      <c r="M18" s="84">
+        <v>1</v>
+      </c>
+      <c r="N18" s="121">
         <v>0</v>
       </c>
-      <c r="O18" s="286"/>
-      <c r="P18" s="286"/>
-      <c r="Q18" s="286"/>
-      <c r="R18" s="286"/>
-      <c r="S18" s="286"/>
-      <c r="T18" s="288" t="s">
+      <c r="O18" s="121"/>
+      <c r="P18" s="121"/>
+      <c r="Q18" s="121"/>
+      <c r="R18" s="121"/>
+      <c r="S18" s="121"/>
+      <c r="T18" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="U18" s="275"/>
-      <c r="V18" s="289"/>
-      <c r="W18" s="290"/>
-      <c r="X18" s="291"/>
-      <c r="Y18" s="291"/>
-      <c r="Z18" s="291"/>
-      <c r="AA18" s="291"/>
-      <c r="AB18" s="291"/>
-      <c r="AC18" s="292"/>
-      <c r="AD18" s="293"/>
-      <c r="AE18" s="280" t="s">
+      <c r="U18" s="84"/>
+      <c r="V18" s="85"/>
+      <c r="W18" s="289"/>
+      <c r="X18" s="290"/>
+      <c r="Y18" s="290"/>
+      <c r="Z18" s="290"/>
+      <c r="AA18" s="290"/>
+      <c r="AB18" s="290"/>
+      <c r="AC18" s="291"/>
+      <c r="AD18" s="292"/>
+      <c r="AE18" s="73" t="s">
         <v>828</v>
       </c>
-      <c r="AF18" s="280" t="s">
+      <c r="AF18" s="73" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="19" spans="1:33" s="270" customFormat="1" ht="17.25">
-      <c r="A19" s="270">
+    <row r="19" spans="1:33" ht="17.25">
+      <c r="A19" s="43">
         <v>18</v>
       </c>
-      <c r="B19" s="270">
+      <c r="B19" s="43">
         <v>2</v>
       </c>
-      <c r="C19" s="283"/>
-      <c r="D19" s="284"/>
-      <c r="E19" s="284"/>
-      <c r="F19" s="283"/>
-      <c r="G19" s="294" t="s">
+      <c r="C19" s="287"/>
+      <c r="D19" s="175"/>
+      <c r="E19" s="175"/>
+      <c r="F19" s="287"/>
+      <c r="G19" s="293" t="s">
         <v>67</v>
       </c>
-      <c r="H19" s="294" t="s">
+      <c r="H19" s="293" t="s">
         <v>67</v>
       </c>
-      <c r="I19" s="287">
+      <c r="I19" s="288">
         <v>19</v>
       </c>
-      <c r="J19" s="287">
-        <v>1</v>
-      </c>
-      <c r="K19" s="275" t="s">
+      <c r="J19" s="288">
+        <v>1</v>
+      </c>
+      <c r="K19" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="L19" s="287" t="s">
+      <c r="L19" s="288" t="s">
         <v>16</v>
       </c>
-      <c r="M19" s="275">
-        <v>1</v>
-      </c>
-      <c r="N19" s="286">
+      <c r="M19" s="84">
+        <v>1</v>
+      </c>
+      <c r="N19" s="121">
         <v>0</v>
       </c>
-      <c r="O19" s="286"/>
-      <c r="P19" s="286"/>
-      <c r="Q19" s="286"/>
-      <c r="R19" s="286"/>
-      <c r="S19" s="286"/>
-      <c r="T19" s="288" t="s">
+      <c r="O19" s="121"/>
+      <c r="P19" s="121"/>
+      <c r="Q19" s="121"/>
+      <c r="R19" s="121"/>
+      <c r="S19" s="121"/>
+      <c r="T19" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="U19" s="275"/>
-      <c r="V19" s="289"/>
-      <c r="W19" s="290"/>
-      <c r="X19" s="291"/>
-      <c r="Y19" s="291"/>
-      <c r="Z19" s="291"/>
-      <c r="AA19" s="291"/>
-      <c r="AB19" s="291"/>
-      <c r="AC19" s="292"/>
-      <c r="AD19" s="293"/>
-      <c r="AE19" s="280" t="s">
+      <c r="U19" s="84"/>
+      <c r="V19" s="85"/>
+      <c r="W19" s="289"/>
+      <c r="X19" s="290"/>
+      <c r="Y19" s="290"/>
+      <c r="Z19" s="290"/>
+      <c r="AA19" s="290"/>
+      <c r="AB19" s="290"/>
+      <c r="AC19" s="291"/>
+      <c r="AD19" s="292"/>
+      <c r="AE19" s="73" t="s">
         <v>828</v>
       </c>
-      <c r="AF19" s="280" t="s">
+      <c r="AF19" s="73" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="20" spans="1:33" s="270" customFormat="1" ht="17.25">
-      <c r="A20" s="270">
+    <row r="20" spans="1:33" ht="17.25">
+      <c r="A20" s="43">
         <v>19</v>
       </c>
-      <c r="B20" s="270">
+      <c r="B20" s="43">
         <v>2</v>
       </c>
-      <c r="C20" s="283"/>
-      <c r="D20" s="284"/>
-      <c r="E20" s="284"/>
-      <c r="F20" s="283"/>
-      <c r="G20" s="294" t="s">
+      <c r="C20" s="287"/>
+      <c r="D20" s="175"/>
+      <c r="E20" s="175"/>
+      <c r="F20" s="287"/>
+      <c r="G20" s="293" t="s">
         <v>68</v>
       </c>
-      <c r="H20" s="294" t="s">
+      <c r="H20" s="293" t="s">
         <v>68</v>
       </c>
-      <c r="I20" s="287">
+      <c r="I20" s="288">
         <v>18</v>
       </c>
-      <c r="J20" s="287">
-        <v>1</v>
-      </c>
-      <c r="K20" s="275" t="s">
+      <c r="J20" s="288">
+        <v>1</v>
+      </c>
+      <c r="K20" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="L20" s="287" t="s">
+      <c r="L20" s="288" t="s">
         <v>16</v>
       </c>
-      <c r="M20" s="275">
-        <v>1</v>
-      </c>
-      <c r="N20" s="286">
+      <c r="M20" s="84">
+        <v>1</v>
+      </c>
+      <c r="N20" s="121">
         <v>0</v>
       </c>
-      <c r="O20" s="286"/>
-      <c r="P20" s="286"/>
-      <c r="Q20" s="286"/>
-      <c r="R20" s="286"/>
-      <c r="S20" s="286"/>
-      <c r="T20" s="288" t="s">
+      <c r="O20" s="121"/>
+      <c r="P20" s="121"/>
+      <c r="Q20" s="121"/>
+      <c r="R20" s="121"/>
+      <c r="S20" s="121"/>
+      <c r="T20" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="U20" s="275"/>
-      <c r="V20" s="289"/>
-      <c r="W20" s="290"/>
-      <c r="X20" s="291"/>
-      <c r="Y20" s="291"/>
-      <c r="Z20" s="291"/>
-      <c r="AA20" s="291"/>
-      <c r="AB20" s="291"/>
-      <c r="AC20" s="292"/>
-      <c r="AD20" s="293"/>
-      <c r="AE20" s="280" t="s">
+      <c r="U20" s="84"/>
+      <c r="V20" s="85"/>
+      <c r="W20" s="289"/>
+      <c r="X20" s="290"/>
+      <c r="Y20" s="290"/>
+      <c r="Z20" s="290"/>
+      <c r="AA20" s="290"/>
+      <c r="AB20" s="290"/>
+      <c r="AC20" s="291"/>
+      <c r="AD20" s="292"/>
+      <c r="AE20" s="73" t="s">
         <v>828</v>
       </c>
-      <c r="AF20" s="280" t="s">
+      <c r="AF20" s="73" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="21" spans="1:33" s="270" customFormat="1" ht="17.25">
-      <c r="A21" s="270">
+    <row r="21" spans="1:33" ht="17.25">
+      <c r="A21" s="43">
         <v>20</v>
       </c>
-      <c r="B21" s="270">
+      <c r="B21" s="43">
         <v>2</v>
       </c>
-      <c r="C21" s="283"/>
-      <c r="D21" s="284"/>
-      <c r="E21" s="284"/>
-      <c r="F21" s="283"/>
-      <c r="G21" s="294" t="s">
+      <c r="C21" s="287"/>
+      <c r="D21" s="175"/>
+      <c r="E21" s="175"/>
+      <c r="F21" s="287"/>
+      <c r="G21" s="293" t="s">
         <v>69</v>
       </c>
-      <c r="H21" s="294" t="s">
+      <c r="H21" s="293" t="s">
         <v>69</v>
       </c>
-      <c r="I21" s="287">
+      <c r="I21" s="288">
         <v>17</v>
       </c>
-      <c r="J21" s="287">
-        <v>1</v>
-      </c>
-      <c r="K21" s="275" t="s">
+      <c r="J21" s="288">
+        <v>1</v>
+      </c>
+      <c r="K21" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="L21" s="287" t="s">
+      <c r="L21" s="288" t="s">
         <v>16</v>
       </c>
-      <c r="M21" s="275">
-        <v>1</v>
-      </c>
-      <c r="N21" s="286">
+      <c r="M21" s="84">
+        <v>1</v>
+      </c>
+      <c r="N21" s="121">
         <v>0</v>
       </c>
-      <c r="O21" s="286"/>
-      <c r="P21" s="286"/>
-      <c r="Q21" s="286"/>
-      <c r="R21" s="286"/>
-      <c r="S21" s="286"/>
-      <c r="T21" s="288" t="s">
+      <c r="O21" s="121"/>
+      <c r="P21" s="121"/>
+      <c r="Q21" s="121"/>
+      <c r="R21" s="121"/>
+      <c r="S21" s="121"/>
+      <c r="T21" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="U21" s="275"/>
-      <c r="V21" s="289"/>
-      <c r="W21" s="290"/>
-      <c r="X21" s="291"/>
-      <c r="Y21" s="291"/>
-      <c r="Z21" s="291"/>
-      <c r="AA21" s="291"/>
-      <c r="AB21" s="291"/>
-      <c r="AC21" s="292"/>
-      <c r="AD21" s="293"/>
-      <c r="AE21" s="280" t="s">
+      <c r="U21" s="84"/>
+      <c r="V21" s="85"/>
+      <c r="W21" s="289"/>
+      <c r="X21" s="290"/>
+      <c r="Y21" s="290"/>
+      <c r="Z21" s="290"/>
+      <c r="AA21" s="290"/>
+      <c r="AB21" s="290"/>
+      <c r="AC21" s="291"/>
+      <c r="AD21" s="292"/>
+      <c r="AE21" s="73" t="s">
         <v>828</v>
       </c>
-      <c r="AF21" s="280" t="s">
+      <c r="AF21" s="73" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="22" spans="1:33" s="270" customFormat="1" ht="18" thickBot="1">
-      <c r="A22" s="270">
+    <row r="22" spans="1:33" ht="18" thickBot="1">
+      <c r="A22" s="43">
         <v>21</v>
       </c>
-      <c r="B22" s="270">
+      <c r="B22" s="43">
         <v>2</v>
       </c>
-      <c r="C22" s="283"/>
-      <c r="D22" s="284"/>
-      <c r="E22" s="284"/>
-      <c r="F22" s="283"/>
-      <c r="G22" s="295" t="s">
+      <c r="C22" s="287"/>
+      <c r="D22" s="175"/>
+      <c r="E22" s="175"/>
+      <c r="F22" s="287"/>
+      <c r="G22" s="294" t="s">
         <v>70</v>
       </c>
-      <c r="H22" s="294" t="s">
+      <c r="H22" s="293" t="s">
         <v>70</v>
       </c>
-      <c r="I22" s="287">
+      <c r="I22" s="288">
         <v>16</v>
       </c>
-      <c r="J22" s="287">
-        <v>1</v>
-      </c>
-      <c r="K22" s="275" t="s">
+      <c r="J22" s="288">
+        <v>1</v>
+      </c>
+      <c r="K22" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="L22" s="287" t="s">
+      <c r="L22" s="288" t="s">
         <v>16</v>
       </c>
-      <c r="M22" s="275">
-        <v>1</v>
-      </c>
-      <c r="N22" s="286">
+      <c r="M22" s="84">
+        <v>1</v>
+      </c>
+      <c r="N22" s="121">
         <v>0</v>
       </c>
-      <c r="O22" s="286"/>
-      <c r="P22" s="286"/>
-      <c r="Q22" s="286"/>
-      <c r="R22" s="286"/>
-      <c r="S22" s="286"/>
-      <c r="T22" s="288" t="s">
+      <c r="O22" s="121"/>
+      <c r="P22" s="121"/>
+      <c r="Q22" s="121"/>
+      <c r="R22" s="121"/>
+      <c r="S22" s="121"/>
+      <c r="T22" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="U22" s="275"/>
-      <c r="V22" s="289"/>
-      <c r="W22" s="290"/>
-      <c r="X22" s="291"/>
-      <c r="Y22" s="291"/>
-      <c r="Z22" s="291"/>
-      <c r="AA22" s="291"/>
-      <c r="AB22" s="291"/>
-      <c r="AC22" s="292"/>
-      <c r="AD22" s="293"/>
-      <c r="AE22" s="280" t="s">
+      <c r="U22" s="84"/>
+      <c r="V22" s="85"/>
+      <c r="W22" s="289"/>
+      <c r="X22" s="290"/>
+      <c r="Y22" s="290"/>
+      <c r="Z22" s="290"/>
+      <c r="AA22" s="290"/>
+      <c r="AB22" s="290"/>
+      <c r="AC22" s="291"/>
+      <c r="AD22" s="292"/>
+      <c r="AE22" s="73" t="s">
         <v>828</v>
       </c>
-      <c r="AF22" s="280" t="s">
+      <c r="AF22" s="73" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="23" spans="1:33" s="270" customFormat="1" ht="18" thickBot="1">
-      <c r="A23" s="270">
+    <row r="23" spans="1:33" ht="18" thickBot="1">
+      <c r="A23" s="43">
         <v>22</v>
       </c>
-      <c r="B23" s="271">
-        <v>1</v>
-      </c>
-      <c r="C23" s="271" t="s">
+      <c r="B23" s="112">
+        <v>1</v>
+      </c>
+      <c r="C23" s="112" t="s">
         <v>392</v>
       </c>
-      <c r="D23" s="272" t="s">
+      <c r="D23" s="114" t="s">
         <v>939</v>
       </c>
-      <c r="E23" s="272" t="s">
+      <c r="E23" s="114" t="s">
         <v>393</v>
       </c>
-      <c r="F23" s="282">
+      <c r="F23" s="113">
         <v>2</v>
       </c>
-      <c r="G23" s="273"/>
-      <c r="H23" s="274"/>
-      <c r="I23" s="272"/>
-      <c r="J23" s="272"/>
-      <c r="K23" s="271" t="s">
+      <c r="G23" s="119"/>
+      <c r="H23" s="117"/>
+      <c r="I23" s="114"/>
+      <c r="J23" s="114"/>
+      <c r="K23" s="112" t="s">
         <v>339</v>
       </c>
-      <c r="L23" s="271" t="s">
+      <c r="L23" s="112" t="s">
         <v>394</v>
       </c>
-      <c r="M23" s="271">
+      <c r="M23" s="112">
         <v>3.90625E-3</v>
       </c>
-      <c r="N23" s="276">
+      <c r="N23" s="174">
         <v>0</v>
       </c>
-      <c r="O23" s="276"/>
-      <c r="P23" s="276"/>
-      <c r="Q23" s="276"/>
-      <c r="R23" s="276"/>
-      <c r="S23" s="276"/>
-      <c r="T23" s="277"/>
-      <c r="U23" s="271"/>
-      <c r="V23" s="278" t="s">
+      <c r="O23" s="174"/>
+      <c r="P23" s="174"/>
+      <c r="Q23" s="174"/>
+      <c r="R23" s="174"/>
+      <c r="S23" s="174"/>
+      <c r="T23" s="209"/>
+      <c r="U23" s="112"/>
+      <c r="V23" s="115" t="s">
         <v>757</v>
       </c>
-      <c r="W23" s="296" t="s">
+      <c r="W23" s="295" t="s">
         <v>37</v>
       </c>
-      <c r="X23" s="271" t="s">
+      <c r="X23" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="Y23" s="271" t="s">
+      <c r="Y23" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="Z23" s="271" t="s">
+      <c r="Z23" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AA23" s="271" t="s">
+      <c r="AA23" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AB23" s="271" t="s">
+      <c r="AB23" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AC23" s="274"/>
-      <c r="AD23" s="272"/>
-      <c r="AE23" s="280"/>
-      <c r="AF23" s="280"/>
-    </row>
-    <row r="24" spans="1:33" s="313" customFormat="1" ht="121.5" thickBot="1">
-      <c r="A24" s="270">
+      <c r="AC23" s="117"/>
+      <c r="AD23" s="114"/>
+      <c r="AE23" s="73"/>
+      <c r="AF23" s="73"/>
+    </row>
+    <row r="24" spans="1:33" s="309" customFormat="1" ht="121.5" thickBot="1">
+      <c r="A24" s="43">
         <v>23</v>
       </c>
-      <c r="B24" s="271">
-        <v>1</v>
-      </c>
-      <c r="C24" s="297" t="s">
+      <c r="B24" s="112">
+        <v>1</v>
+      </c>
+      <c r="C24" s="296" t="s">
         <v>555</v>
       </c>
-      <c r="D24" s="298" t="s">
+      <c r="D24" s="297" t="s">
         <v>556</v>
       </c>
-      <c r="E24" s="299" t="s">
+      <c r="E24" s="298" t="s">
         <v>557</v>
       </c>
-      <c r="F24" s="300">
-        <v>1</v>
-      </c>
-      <c r="G24" s="301"/>
-      <c r="H24" s="302"/>
-      <c r="I24" s="303"/>
-      <c r="J24" s="303"/>
-      <c r="K24" s="275"/>
-      <c r="L24" s="304" t="s">
+      <c r="F24" s="299">
+        <v>1</v>
+      </c>
+      <c r="G24" s="300"/>
+      <c r="H24" s="301"/>
+      <c r="I24" s="302"/>
+      <c r="J24" s="302"/>
+      <c r="K24" s="84"/>
+      <c r="L24" s="303" t="s">
         <v>16</v>
       </c>
-      <c r="M24" s="297">
-        <v>1</v>
-      </c>
-      <c r="N24" s="305">
+      <c r="M24" s="296">
+        <v>1</v>
+      </c>
+      <c r="N24" s="304">
         <v>0</v>
       </c>
-      <c r="O24" s="303"/>
-      <c r="P24" s="303"/>
-      <c r="Q24" s="303"/>
-      <c r="R24" s="303"/>
-      <c r="S24" s="303"/>
-      <c r="T24" s="306" t="s">
+      <c r="O24" s="302"/>
+      <c r="P24" s="302"/>
+      <c r="Q24" s="302"/>
+      <c r="R24" s="302"/>
+      <c r="S24" s="302"/>
+      <c r="T24" s="305" t="s">
         <v>558</v>
       </c>
-      <c r="U24" s="307"/>
-      <c r="V24" s="308" t="s">
+      <c r="U24" s="47"/>
+      <c r="V24" s="81" t="s">
         <v>753</v>
       </c>
-      <c r="W24" s="309" t="s">
+      <c r="W24" s="306" t="s">
         <v>37</v>
       </c>
-      <c r="X24" s="271" t="s">
+      <c r="X24" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="Y24" s="271" t="s">
+      <c r="Y24" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="Z24" s="271" t="s">
+      <c r="Z24" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AA24" s="271" t="s">
+      <c r="AA24" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB24" s="271" t="s">
+      <c r="AB24" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AC24" s="310"/>
-      <c r="AD24" s="311"/>
-      <c r="AE24" s="280" t="s">
+      <c r="AC24" s="307"/>
+      <c r="AD24" s="308"/>
+      <c r="AE24" s="73" t="s">
         <v>829</v>
       </c>
-      <c r="AF24" s="280" t="s">
+      <c r="AF24" s="73" t="s">
         <v>743</v>
       </c>
-      <c r="AG24" s="312" t="s">
+      <c r="AG24" s="55" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="25" spans="1:33" s="313" customFormat="1" ht="35.25" thickBot="1">
-      <c r="A25" s="270">
+    <row r="25" spans="1:33" s="309" customFormat="1" ht="35.25" thickBot="1">
+      <c r="A25" s="43">
         <v>24</v>
       </c>
-      <c r="B25" s="271">
-        <v>1</v>
-      </c>
-      <c r="C25" s="314" t="s">
+      <c r="B25" s="112">
+        <v>1</v>
+      </c>
+      <c r="C25" s="310" t="s">
         <v>559</v>
       </c>
-      <c r="D25" s="315" t="s">
+      <c r="D25" s="311" t="s">
         <v>560</v>
       </c>
-      <c r="E25" s="315" t="s">
+      <c r="E25" s="311" t="s">
         <v>561</v>
       </c>
-      <c r="F25" s="300">
-        <v>1</v>
-      </c>
-      <c r="G25" s="301"/>
-      <c r="H25" s="302"/>
-      <c r="I25" s="303"/>
-      <c r="J25" s="303"/>
-      <c r="K25" s="270"/>
-      <c r="L25" s="304" t="s">
+      <c r="F25" s="299">
+        <v>1</v>
+      </c>
+      <c r="G25" s="300"/>
+      <c r="H25" s="301"/>
+      <c r="I25" s="302"/>
+      <c r="J25" s="302"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="303" t="s">
         <v>16</v>
       </c>
-      <c r="M25" s="297">
-        <v>1</v>
-      </c>
-      <c r="N25" s="305">
+      <c r="M25" s="296">
+        <v>1</v>
+      </c>
+      <c r="N25" s="304">
         <v>0</v>
       </c>
-      <c r="O25" s="303"/>
-      <c r="P25" s="303"/>
-      <c r="Q25" s="303"/>
-      <c r="R25" s="303"/>
-      <c r="S25" s="303"/>
-      <c r="T25" s="306" t="s">
+      <c r="O25" s="302"/>
+      <c r="P25" s="302"/>
+      <c r="Q25" s="302"/>
+      <c r="R25" s="302"/>
+      <c r="S25" s="302"/>
+      <c r="T25" s="305" t="s">
         <v>562</v>
       </c>
-      <c r="U25" s="307"/>
-      <c r="V25" s="308" t="s">
+      <c r="U25" s="47"/>
+      <c r="V25" s="81" t="s">
         <v>753</v>
       </c>
-      <c r="W25" s="309" t="s">
+      <c r="W25" s="306" t="s">
         <v>37</v>
       </c>
-      <c r="X25" s="271" t="s">
+      <c r="X25" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="Y25" s="271" t="s">
+      <c r="Y25" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="Z25" s="271" t="s">
+      <c r="Z25" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AA25" s="271" t="s">
+      <c r="AA25" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB25" s="271" t="s">
+      <c r="AB25" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AC25" s="310"/>
-      <c r="AD25" s="311"/>
-      <c r="AE25" s="280" t="s">
+      <c r="AC25" s="307"/>
+      <c r="AD25" s="308"/>
+      <c r="AE25" s="73" t="s">
         <v>741</v>
       </c>
-      <c r="AF25" s="280" t="s">
+      <c r="AF25" s="73" t="s">
         <v>828</v>
       </c>
-      <c r="AG25" s="312"/>
-    </row>
-    <row r="26" spans="1:33" s="313" customFormat="1" ht="69.75" thickBot="1">
-      <c r="A26" s="270">
+      <c r="AG25" s="55"/>
+    </row>
+    <row r="26" spans="1:33" s="309" customFormat="1" ht="69.75" thickBot="1">
+      <c r="A26" s="43">
         <v>25</v>
       </c>
-      <c r="B26" s="271">
-        <v>1</v>
-      </c>
-      <c r="C26" s="314" t="s">
+      <c r="B26" s="112">
+        <v>1</v>
+      </c>
+      <c r="C26" s="310" t="s">
         <v>563</v>
       </c>
-      <c r="D26" s="315" t="s">
+      <c r="D26" s="311" t="s">
         <v>564</v>
       </c>
-      <c r="E26" s="315" t="s">
+      <c r="E26" s="311" t="s">
         <v>565</v>
       </c>
-      <c r="F26" s="300">
-        <v>1</v>
-      </c>
-      <c r="G26" s="301"/>
-      <c r="H26" s="302"/>
-      <c r="I26" s="303"/>
-      <c r="J26" s="303"/>
-      <c r="K26" s="270"/>
-      <c r="L26" s="304" t="s">
+      <c r="F26" s="299">
+        <v>1</v>
+      </c>
+      <c r="G26" s="300"/>
+      <c r="H26" s="301"/>
+      <c r="I26" s="302"/>
+      <c r="J26" s="302"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="303" t="s">
         <v>16</v>
       </c>
-      <c r="M26" s="297">
-        <v>1</v>
-      </c>
-      <c r="N26" s="305">
+      <c r="M26" s="296">
+        <v>1</v>
+      </c>
+      <c r="N26" s="304">
         <v>0</v>
       </c>
-      <c r="O26" s="303"/>
-      <c r="P26" s="303"/>
-      <c r="Q26" s="303"/>
-      <c r="R26" s="303"/>
-      <c r="S26" s="303"/>
-      <c r="T26" s="306" t="s">
+      <c r="O26" s="302"/>
+      <c r="P26" s="302"/>
+      <c r="Q26" s="302"/>
+      <c r="R26" s="302"/>
+      <c r="S26" s="302"/>
+      <c r="T26" s="305" t="s">
         <v>566</v>
       </c>
-      <c r="U26" s="307"/>
-      <c r="V26" s="308" t="s">
+      <c r="U26" s="47"/>
+      <c r="V26" s="81" t="s">
         <v>753</v>
       </c>
-      <c r="W26" s="309" t="s">
+      <c r="W26" s="306" t="s">
         <v>37</v>
       </c>
-      <c r="X26" s="271" t="s">
+      <c r="X26" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="Y26" s="271" t="s">
+      <c r="Y26" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="Z26" s="271" t="s">
+      <c r="Z26" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AA26" s="271" t="s">
+      <c r="AA26" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB26" s="271" t="s">
+      <c r="AB26" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AC26" s="310"/>
-      <c r="AD26" s="311"/>
-      <c r="AE26" s="280" t="s">
+      <c r="AC26" s="307"/>
+      <c r="AD26" s="308"/>
+      <c r="AE26" s="73" t="s">
         <v>741</v>
       </c>
-      <c r="AF26" s="280" t="s">
+      <c r="AF26" s="73" t="s">
         <v>741</v>
       </c>
-      <c r="AG26" s="312"/>
-    </row>
-    <row r="27" spans="1:33" s="313" customFormat="1" ht="18" thickBot="1">
-      <c r="A27" s="270">
+      <c r="AG26" s="55"/>
+    </row>
+    <row r="27" spans="1:33" s="309" customFormat="1" ht="18" thickBot="1">
+      <c r="A27" s="43">
         <v>26</v>
       </c>
-      <c r="B27" s="271">
-        <v>1</v>
-      </c>
-      <c r="C27" s="314" t="s">
+      <c r="B27" s="112">
+        <v>1</v>
+      </c>
+      <c r="C27" s="310" t="s">
         <v>567</v>
       </c>
-      <c r="D27" s="315" t="s">
+      <c r="D27" s="311" t="s">
         <v>568</v>
       </c>
-      <c r="E27" s="315" t="s">
+      <c r="E27" s="311" t="s">
         <v>569</v>
       </c>
-      <c r="F27" s="300">
-        <v>1</v>
-      </c>
-      <c r="G27" s="301"/>
-      <c r="H27" s="316"/>
-      <c r="I27" s="317"/>
-      <c r="J27" s="317"/>
-      <c r="K27" s="270"/>
-      <c r="L27" s="318" t="s">
+      <c r="F27" s="299">
+        <v>1</v>
+      </c>
+      <c r="G27" s="300"/>
+      <c r="H27" s="312"/>
+      <c r="I27" s="313"/>
+      <c r="J27" s="313"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="314" t="s">
         <v>16</v>
       </c>
-      <c r="M27" s="319">
-        <v>1</v>
-      </c>
-      <c r="N27" s="320">
+      <c r="M27" s="315">
+        <v>1</v>
+      </c>
+      <c r="N27" s="316">
         <v>0</v>
       </c>
-      <c r="O27" s="317"/>
-      <c r="P27" s="317"/>
-      <c r="Q27" s="317"/>
-      <c r="R27" s="317"/>
-      <c r="S27" s="317"/>
-      <c r="T27" s="321" t="s">
+      <c r="O27" s="313"/>
+      <c r="P27" s="313"/>
+      <c r="Q27" s="313"/>
+      <c r="R27" s="313"/>
+      <c r="S27" s="313"/>
+      <c r="T27" s="317" t="s">
         <v>570</v>
       </c>
-      <c r="U27" s="322"/>
-      <c r="V27" s="308" t="s">
+      <c r="U27" s="318"/>
+      <c r="V27" s="81" t="s">
         <v>753</v>
       </c>
-      <c r="W27" s="323" t="s">
+      <c r="W27" s="319" t="s">
         <v>37</v>
       </c>
-      <c r="X27" s="271" t="s">
+      <c r="X27" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="Y27" s="271" t="s">
+      <c r="Y27" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="Z27" s="271" t="s">
+      <c r="Z27" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AA27" s="271" t="s">
+      <c r="AA27" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB27" s="271" t="s">
+      <c r="AB27" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AC27" s="324"/>
-      <c r="AD27" s="325"/>
-      <c r="AE27" s="280" t="s">
+      <c r="AC27" s="320"/>
+      <c r="AD27" s="321"/>
+      <c r="AE27" s="73" t="s">
         <v>828</v>
       </c>
-      <c r="AF27" s="280" t="s">
+      <c r="AF27" s="73" t="s">
         <v>741</v>
       </c>
-      <c r="AG27" s="312"/>
-    </row>
-    <row r="28" spans="1:33" s="270" customFormat="1" ht="18" thickBot="1">
-      <c r="A28" s="270">
+      <c r="AG27" s="55"/>
+    </row>
+    <row r="28" spans="1:33" ht="18" thickBot="1">
+      <c r="A28" s="43">
         <v>27</v>
       </c>
-      <c r="B28" s="271">
-        <v>1</v>
-      </c>
-      <c r="C28" s="307" t="s">
+      <c r="B28" s="112">
+        <v>1</v>
+      </c>
+      <c r="C28" s="47" t="s">
         <v>790</v>
       </c>
-      <c r="D28" s="326" t="s">
+      <c r="D28" s="94" t="s">
         <v>571</v>
       </c>
-      <c r="E28" s="326" t="s">
+      <c r="E28" s="94" t="s">
         <v>572</v>
       </c>
-      <c r="F28" s="327">
+      <c r="F28" s="82">
         <v>5</v>
       </c>
-      <c r="G28" s="328"/>
-      <c r="H28" s="329"/>
-      <c r="I28" s="330"/>
-      <c r="J28" s="330"/>
-      <c r="K28" s="330"/>
-      <c r="L28" s="330" t="s">
+      <c r="G28" s="86"/>
+      <c r="H28" s="87"/>
+      <c r="I28" s="83"/>
+      <c r="J28" s="83"/>
+      <c r="K28" s="83"/>
+      <c r="L28" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="M28" s="307"/>
-      <c r="N28" s="303"/>
-      <c r="O28" s="303"/>
-      <c r="P28" s="303"/>
-      <c r="Q28" s="303"/>
-      <c r="R28" s="303"/>
-      <c r="S28" s="303"/>
-      <c r="T28" s="326"/>
-      <c r="U28" s="307"/>
-      <c r="V28" s="308" t="s">
+      <c r="M28" s="47"/>
+      <c r="N28" s="302"/>
+      <c r="O28" s="302"/>
+      <c r="P28" s="302"/>
+      <c r="Q28" s="302"/>
+      <c r="R28" s="302"/>
+      <c r="S28" s="302"/>
+      <c r="T28" s="94"/>
+      <c r="U28" s="47"/>
+      <c r="V28" s="81" t="s">
         <v>753</v>
       </c>
-      <c r="W28" s="331" t="s">
+      <c r="W28" s="322" t="s">
         <v>37</v>
       </c>
-      <c r="X28" s="271" t="s">
+      <c r="X28" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="Y28" s="271" t="s">
+      <c r="Y28" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="Z28" s="271" t="s">
+      <c r="Z28" s="112" t="s">
         <v>757</v>
       </c>
-      <c r="AA28" s="271" t="s">
+      <c r="AA28" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB28" s="271" t="s">
+      <c r="AB28" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AC28" s="329"/>
-      <c r="AD28" s="326"/>
-      <c r="AE28" s="280"/>
-      <c r="AF28" s="280"/>
-    </row>
-    <row r="29" spans="1:33" s="270" customFormat="1" ht="34.5">
-      <c r="A29" s="270">
+      <c r="AC28" s="87"/>
+      <c r="AD28" s="94"/>
+      <c r="AE28" s="73"/>
+      <c r="AF28" s="73"/>
+    </row>
+    <row r="29" spans="1:33" ht="34.5">
+      <c r="A29" s="43">
         <v>28</v>
       </c>
-      <c r="B29" s="270">
+      <c r="B29" s="43">
         <v>2</v>
       </c>
-      <c r="D29" s="332"/>
-      <c r="E29" s="332"/>
-      <c r="G29" s="333" t="s">
+      <c r="D29" s="65"/>
+      <c r="G29" s="88" t="s">
         <v>627</v>
       </c>
-      <c r="H29" s="333" t="s">
+      <c r="H29" s="88" t="s">
         <v>573</v>
       </c>
-      <c r="I29" s="334">
+      <c r="I29" s="75">
         <v>0</v>
       </c>
-      <c r="J29" s="334">
-        <v>1</v>
-      </c>
-      <c r="K29" s="334" t="s">
+      <c r="J29" s="75">
+        <v>1</v>
+      </c>
+      <c r="K29" s="75" t="s">
         <v>467</v>
       </c>
-      <c r="L29" s="334" t="s">
+      <c r="L29" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="M29" s="334">
-        <v>1</v>
-      </c>
-      <c r="N29" s="285">
+      <c r="M29" s="75">
+        <v>1</v>
+      </c>
+      <c r="N29" s="120">
         <v>0</v>
       </c>
-      <c r="O29" s="285"/>
-      <c r="P29" s="285"/>
-      <c r="Q29" s="285"/>
-      <c r="R29" s="285"/>
-      <c r="S29" s="285"/>
-      <c r="T29" s="335" t="s">
+      <c r="O29" s="120"/>
+      <c r="P29" s="120"/>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="120"/>
+      <c r="S29" s="120"/>
+      <c r="T29" s="323" t="s">
         <v>574</v>
       </c>
-      <c r="U29" s="334"/>
-      <c r="V29" s="336"/>
-      <c r="W29" s="337"/>
-      <c r="X29" s="291"/>
-      <c r="Y29" s="291"/>
-      <c r="Z29" s="291"/>
-      <c r="AA29" s="291"/>
-      <c r="AB29" s="291"/>
-      <c r="AC29" s="338"/>
-      <c r="AD29" s="336"/>
-      <c r="AE29" s="280" t="s">
+      <c r="U29" s="75"/>
+      <c r="V29" s="95"/>
+      <c r="W29" s="324"/>
+      <c r="X29" s="290"/>
+      <c r="Y29" s="290"/>
+      <c r="Z29" s="290"/>
+      <c r="AA29" s="290"/>
+      <c r="AB29" s="290"/>
+      <c r="AC29" s="96"/>
+      <c r="AD29" s="95"/>
+      <c r="AE29" s="73" t="s">
         <v>741</v>
       </c>
-      <c r="AF29" s="280" t="s">
+      <c r="AF29" s="73" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="30" spans="1:33" s="270" customFormat="1" ht="34.5">
-      <c r="A30" s="270">
+    <row r="30" spans="1:33" ht="34.5">
+      <c r="A30" s="43">
         <v>29</v>
       </c>
-      <c r="B30" s="270">
+      <c r="B30" s="43">
         <v>2</v>
       </c>
-      <c r="D30" s="332"/>
-      <c r="E30" s="332"/>
-      <c r="G30" s="339" t="s">
+      <c r="D30" s="65"/>
+      <c r="G30" s="32" t="s">
         <v>628</v>
       </c>
-      <c r="H30" s="339" t="s">
+      <c r="H30" s="32" t="s">
         <v>575</v>
       </c>
-      <c r="I30" s="275">
-        <v>1</v>
-      </c>
-      <c r="J30" s="275">
-        <v>1</v>
-      </c>
-      <c r="K30" s="275" t="s">
+      <c r="I30" s="84">
+        <v>1</v>
+      </c>
+      <c r="J30" s="84">
+        <v>1</v>
+      </c>
+      <c r="K30" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L30" s="275" t="s">
+      <c r="L30" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M30" s="275">
-        <v>1</v>
-      </c>
-      <c r="N30" s="286">
+      <c r="M30" s="84">
+        <v>1</v>
+      </c>
+      <c r="N30" s="121">
         <v>0</v>
       </c>
-      <c r="O30" s="286"/>
-      <c r="P30" s="286"/>
-      <c r="Q30" s="286"/>
-      <c r="R30" s="286"/>
-      <c r="S30" s="286"/>
-      <c r="T30" s="288" t="s">
+      <c r="O30" s="121"/>
+      <c r="P30" s="121"/>
+      <c r="Q30" s="121"/>
+      <c r="R30" s="121"/>
+      <c r="S30" s="121"/>
+      <c r="T30" s="33" t="s">
         <v>576</v>
       </c>
-      <c r="U30" s="275"/>
-      <c r="V30" s="336"/>
-      <c r="W30" s="290"/>
-      <c r="X30" s="291"/>
-      <c r="Y30" s="291"/>
-      <c r="Z30" s="291"/>
-      <c r="AA30" s="291"/>
-      <c r="AB30" s="291"/>
-      <c r="AC30" s="340"/>
-      <c r="AD30" s="289"/>
-      <c r="AE30" s="280" t="s">
+      <c r="U30" s="84"/>
+      <c r="V30" s="95"/>
+      <c r="W30" s="289"/>
+      <c r="X30" s="290"/>
+      <c r="Y30" s="290"/>
+      <c r="Z30" s="290"/>
+      <c r="AA30" s="290"/>
+      <c r="AB30" s="290"/>
+      <c r="AC30" s="72"/>
+      <c r="AD30" s="85"/>
+      <c r="AE30" s="73" t="s">
         <v>828</v>
       </c>
-      <c r="AF30" s="280" t="s">
+      <c r="AF30" s="73" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="31" spans="1:33" s="270" customFormat="1" ht="34.5">
-      <c r="A31" s="270">
+    <row r="31" spans="1:33" ht="34.5">
+      <c r="A31" s="43">
         <v>30</v>
       </c>
-      <c r="B31" s="270">
+      <c r="B31" s="43">
         <v>2</v>
       </c>
-      <c r="D31" s="332"/>
-      <c r="E31" s="332"/>
-      <c r="G31" s="339" t="s">
+      <c r="D31" s="65"/>
+      <c r="G31" s="32" t="s">
         <v>629</v>
       </c>
-      <c r="H31" s="339" t="s">
+      <c r="H31" s="32" t="s">
         <v>577</v>
       </c>
-      <c r="I31" s="275">
+      <c r="I31" s="84">
         <v>2</v>
       </c>
-      <c r="J31" s="275">
-        <v>1</v>
-      </c>
-      <c r="K31" s="275" t="s">
+      <c r="J31" s="84">
+        <v>1</v>
+      </c>
+      <c r="K31" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L31" s="275" t="s">
+      <c r="L31" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M31" s="275">
-        <v>1</v>
-      </c>
-      <c r="N31" s="286">
+      <c r="M31" s="84">
+        <v>1</v>
+      </c>
+      <c r="N31" s="121">
         <v>0</v>
       </c>
-      <c r="O31" s="286"/>
-      <c r="P31" s="286"/>
-      <c r="Q31" s="286"/>
-      <c r="R31" s="286"/>
-      <c r="S31" s="286"/>
-      <c r="T31" s="288" t="s">
+      <c r="O31" s="121"/>
+      <c r="P31" s="121"/>
+      <c r="Q31" s="121"/>
+      <c r="R31" s="121"/>
+      <c r="S31" s="121"/>
+      <c r="T31" s="33" t="s">
         <v>578</v>
       </c>
-      <c r="U31" s="275"/>
-      <c r="V31" s="336"/>
-      <c r="W31" s="290"/>
-      <c r="X31" s="291"/>
-      <c r="Y31" s="291"/>
-      <c r="Z31" s="291"/>
-      <c r="AA31" s="291"/>
-      <c r="AB31" s="291"/>
-      <c r="AC31" s="340"/>
-      <c r="AD31" s="289"/>
-      <c r="AE31" s="280" t="s">
+      <c r="U31" s="84"/>
+      <c r="V31" s="95"/>
+      <c r="W31" s="289"/>
+      <c r="X31" s="290"/>
+      <c r="Y31" s="290"/>
+      <c r="Z31" s="290"/>
+      <c r="AA31" s="290"/>
+      <c r="AB31" s="290"/>
+      <c r="AC31" s="72"/>
+      <c r="AD31" s="85"/>
+      <c r="AE31" s="73" t="s">
         <v>741</v>
       </c>
-      <c r="AF31" s="280" t="s">
+      <c r="AF31" s="73" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="32" spans="1:33" s="270" customFormat="1" ht="17.25">
-      <c r="A32" s="270">
+    <row r="32" spans="1:33" ht="17.25">
+      <c r="A32" s="43">
         <v>31</v>
       </c>
-      <c r="B32" s="270">
+      <c r="B32" s="43">
         <v>2</v>
       </c>
-      <c r="D32" s="332"/>
-      <c r="E32" s="332"/>
-      <c r="G32" s="339" t="s">
+      <c r="D32" s="65"/>
+      <c r="G32" s="32" t="s">
         <v>617</v>
       </c>
-      <c r="H32" s="339" t="s">
+      <c r="H32" s="32" t="s">
         <v>614</v>
       </c>
-      <c r="I32" s="275">
+      <c r="I32" s="84">
         <v>3</v>
       </c>
-      <c r="J32" s="275">
-        <v>1</v>
-      </c>
-      <c r="K32" s="275" t="s">
+      <c r="J32" s="84">
+        <v>1</v>
+      </c>
+      <c r="K32" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L32" s="275" t="s">
+      <c r="L32" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M32" s="275">
-        <v>1</v>
-      </c>
-      <c r="N32" s="286">
+      <c r="M32" s="84">
+        <v>1</v>
+      </c>
+      <c r="N32" s="121">
         <v>0</v>
       </c>
-      <c r="O32" s="286"/>
-      <c r="P32" s="286"/>
-      <c r="Q32" s="286"/>
-      <c r="R32" s="286"/>
-      <c r="S32" s="286"/>
-      <c r="T32" s="288" t="s">
+      <c r="O32" s="121"/>
+      <c r="P32" s="121"/>
+      <c r="Q32" s="121"/>
+      <c r="R32" s="121"/>
+      <c r="S32" s="121"/>
+      <c r="T32" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="U32" s="275"/>
-      <c r="V32" s="336"/>
-      <c r="W32" s="290"/>
-      <c r="X32" s="291"/>
-      <c r="Y32" s="291"/>
-      <c r="Z32" s="291"/>
-      <c r="AA32" s="291"/>
-      <c r="AB32" s="291"/>
-      <c r="AC32" s="340"/>
-      <c r="AD32" s="289"/>
-      <c r="AE32" s="280" t="s">
+      <c r="U32" s="84"/>
+      <c r="V32" s="95"/>
+      <c r="W32" s="289"/>
+      <c r="X32" s="290"/>
+      <c r="Y32" s="290"/>
+      <c r="Z32" s="290"/>
+      <c r="AA32" s="290"/>
+      <c r="AB32" s="290"/>
+      <c r="AC32" s="72"/>
+      <c r="AD32" s="85"/>
+      <c r="AE32" s="73" t="s">
         <v>828</v>
       </c>
-      <c r="AF32" s="280" t="s">
+      <c r="AF32" s="73" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="33" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A33" s="270">
+    <row r="33" spans="1:32" ht="17.25">
+      <c r="A33" s="43">
         <v>32</v>
       </c>
-      <c r="B33" s="270">
+      <c r="B33" s="43">
         <v>2</v>
       </c>
-      <c r="D33" s="332"/>
-      <c r="E33" s="332"/>
-      <c r="G33" s="339" t="s">
+      <c r="D33" s="65"/>
+      <c r="G33" s="32" t="s">
         <v>580</v>
       </c>
-      <c r="H33" s="339" t="s">
+      <c r="H33" s="32" t="s">
         <v>615</v>
       </c>
-      <c r="I33" s="275">
+      <c r="I33" s="84">
         <v>4</v>
       </c>
-      <c r="J33" s="275">
-        <v>1</v>
-      </c>
-      <c r="K33" s="275" t="s">
+      <c r="J33" s="84">
+        <v>1</v>
+      </c>
+      <c r="K33" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L33" s="275" t="s">
+      <c r="L33" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M33" s="275">
-        <v>1</v>
-      </c>
-      <c r="N33" s="286">
+      <c r="M33" s="84">
+        <v>1</v>
+      </c>
+      <c r="N33" s="121">
         <v>0</v>
       </c>
-      <c r="O33" s="286"/>
-      <c r="P33" s="286"/>
-      <c r="Q33" s="286"/>
-      <c r="R33" s="286"/>
-      <c r="S33" s="286"/>
-      <c r="T33" s="288" t="s">
+      <c r="O33" s="121"/>
+      <c r="P33" s="121"/>
+      <c r="Q33" s="121"/>
+      <c r="R33" s="121"/>
+      <c r="S33" s="121"/>
+      <c r="T33" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="U33" s="275"/>
-      <c r="V33" s="336"/>
-      <c r="W33" s="290"/>
-      <c r="X33" s="291"/>
-      <c r="Y33" s="291"/>
-      <c r="Z33" s="291"/>
-      <c r="AA33" s="291"/>
-      <c r="AB33" s="291"/>
-      <c r="AC33" s="340"/>
-      <c r="AD33" s="289"/>
-      <c r="AE33" s="280" t="s">
+      <c r="U33" s="84"/>
+      <c r="V33" s="95"/>
+      <c r="W33" s="289"/>
+      <c r="X33" s="290"/>
+      <c r="Y33" s="290"/>
+      <c r="Z33" s="290"/>
+      <c r="AA33" s="290"/>
+      <c r="AB33" s="290"/>
+      <c r="AC33" s="72"/>
+      <c r="AD33" s="85"/>
+      <c r="AE33" s="73" t="s">
         <v>828</v>
       </c>
-      <c r="AF33" s="280" t="s">
+      <c r="AF33" s="73" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="34" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A34" s="270">
+    <row r="34" spans="1:32" ht="17.25">
+      <c r="A34" s="43">
         <v>33</v>
       </c>
-      <c r="B34" s="270">
+      <c r="B34" s="43">
         <v>2</v>
       </c>
-      <c r="D34" s="332"/>
-      <c r="E34" s="332"/>
-      <c r="G34" s="339" t="s">
+      <c r="D34" s="65"/>
+      <c r="G34" s="32" t="s">
         <v>581</v>
       </c>
-      <c r="H34" s="339" t="s">
+      <c r="H34" s="32" t="s">
         <v>616</v>
       </c>
-      <c r="I34" s="275">
+      <c r="I34" s="84">
         <v>5</v>
       </c>
-      <c r="J34" s="275">
-        <v>1</v>
-      </c>
-      <c r="K34" s="275" t="s">
+      <c r="J34" s="84">
+        <v>1</v>
+      </c>
+      <c r="K34" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L34" s="275" t="s">
+      <c r="L34" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M34" s="275">
-        <v>1</v>
-      </c>
-      <c r="N34" s="286">
+      <c r="M34" s="84">
+        <v>1</v>
+      </c>
+      <c r="N34" s="121">
         <v>0</v>
       </c>
-      <c r="O34" s="286"/>
-      <c r="P34" s="286"/>
-      <c r="Q34" s="286"/>
-      <c r="R34" s="286"/>
-      <c r="S34" s="286"/>
-      <c r="T34" s="288" t="s">
+      <c r="O34" s="121"/>
+      <c r="P34" s="121"/>
+      <c r="Q34" s="121"/>
+      <c r="R34" s="121"/>
+      <c r="S34" s="121"/>
+      <c r="T34" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="U34" s="275"/>
-      <c r="V34" s="336"/>
-      <c r="W34" s="290"/>
-      <c r="X34" s="291"/>
-      <c r="Y34" s="291"/>
-      <c r="Z34" s="291"/>
-      <c r="AA34" s="291"/>
-      <c r="AB34" s="291"/>
-      <c r="AC34" s="340"/>
-      <c r="AD34" s="289"/>
-      <c r="AE34" s="280" t="s">
+      <c r="U34" s="84"/>
+      <c r="V34" s="95"/>
+      <c r="W34" s="289"/>
+      <c r="X34" s="290"/>
+      <c r="Y34" s="290"/>
+      <c r="Z34" s="290"/>
+      <c r="AA34" s="290"/>
+      <c r="AB34" s="290"/>
+      <c r="AC34" s="72"/>
+      <c r="AD34" s="85"/>
+      <c r="AE34" s="73" t="s">
         <v>828</v>
       </c>
-      <c r="AF34" s="280" t="s">
+      <c r="AF34" s="73" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="35" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A35" s="270">
+    <row r="35" spans="1:32" ht="17.25">
+      <c r="A35" s="43">
         <v>34</v>
       </c>
-      <c r="B35" s="270">
+      <c r="B35" s="43">
         <v>2</v>
       </c>
-      <c r="D35" s="332"/>
-      <c r="E35" s="332"/>
-      <c r="G35" s="339" t="s">
+      <c r="D35" s="65"/>
+      <c r="G35" s="32" t="s">
         <v>630</v>
       </c>
-      <c r="H35" s="339" t="s">
+      <c r="H35" s="32" t="s">
         <v>582</v>
       </c>
-      <c r="I35" s="275">
+      <c r="I35" s="84">
         <v>6</v>
       </c>
-      <c r="J35" s="275">
-        <v>1</v>
-      </c>
-      <c r="K35" s="275" t="s">
+      <c r="J35" s="84">
+        <v>1</v>
+      </c>
+      <c r="K35" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L35" s="275" t="s">
+      <c r="L35" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M35" s="275">
-        <v>1</v>
-      </c>
-      <c r="N35" s="286">
+      <c r="M35" s="84">
+        <v>1</v>
+      </c>
+      <c r="N35" s="121">
         <v>0</v>
       </c>
-      <c r="O35" s="286"/>
-      <c r="P35" s="286"/>
-      <c r="Q35" s="286"/>
-      <c r="R35" s="286"/>
-      <c r="S35" s="286"/>
-      <c r="T35" s="288" t="s">
+      <c r="O35" s="121"/>
+      <c r="P35" s="121"/>
+      <c r="Q35" s="121"/>
+      <c r="R35" s="121"/>
+      <c r="S35" s="121"/>
+      <c r="T35" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="U35" s="275"/>
-      <c r="V35" s="336"/>
-      <c r="W35" s="290"/>
-      <c r="X35" s="291"/>
-      <c r="Y35" s="291"/>
-      <c r="Z35" s="291"/>
-      <c r="AA35" s="291"/>
-      <c r="AB35" s="291"/>
-      <c r="AC35" s="340"/>
-      <c r="AD35" s="289"/>
-      <c r="AE35" s="280" t="s">
+      <c r="U35" s="84"/>
+      <c r="V35" s="95"/>
+      <c r="W35" s="289"/>
+      <c r="X35" s="290"/>
+      <c r="Y35" s="290"/>
+      <c r="Z35" s="290"/>
+      <c r="AA35" s="290"/>
+      <c r="AB35" s="290"/>
+      <c r="AC35" s="72"/>
+      <c r="AD35" s="85"/>
+      <c r="AE35" s="73" t="s">
         <v>741</v>
       </c>
-      <c r="AF35" s="280" t="s">
+      <c r="AF35" s="73" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="36" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A36" s="270">
+    <row r="36" spans="1:32" ht="17.25">
+      <c r="A36" s="43">
         <v>35</v>
       </c>
-      <c r="B36" s="270">
+      <c r="B36" s="43">
         <v>2</v>
       </c>
-      <c r="D36" s="332"/>
-      <c r="E36" s="332"/>
-      <c r="G36" s="339" t="s">
+      <c r="D36" s="65"/>
+      <c r="G36" s="32" t="s">
         <v>631</v>
       </c>
-      <c r="H36" s="339" t="s">
+      <c r="H36" s="32" t="s">
         <v>583</v>
       </c>
-      <c r="I36" s="275">
+      <c r="I36" s="84">
         <v>7</v>
       </c>
-      <c r="J36" s="275">
-        <v>1</v>
-      </c>
-      <c r="K36" s="275" t="s">
+      <c r="J36" s="84">
+        <v>1</v>
+      </c>
+      <c r="K36" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L36" s="275" t="s">
+      <c r="L36" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M36" s="275">
-        <v>1</v>
-      </c>
-      <c r="N36" s="286">
+      <c r="M36" s="84">
+        <v>1</v>
+      </c>
+      <c r="N36" s="121">
         <v>0</v>
       </c>
-      <c r="O36" s="286"/>
-      <c r="P36" s="286"/>
-      <c r="Q36" s="286"/>
-      <c r="R36" s="286"/>
-      <c r="S36" s="286"/>
-      <c r="T36" s="288" t="s">
+      <c r="O36" s="121"/>
+      <c r="P36" s="121"/>
+      <c r="Q36" s="121"/>
+      <c r="R36" s="121"/>
+      <c r="S36" s="121"/>
+      <c r="T36" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="U36" s="275"/>
-      <c r="V36" s="336"/>
-      <c r="W36" s="290"/>
-      <c r="X36" s="291"/>
-      <c r="Y36" s="291"/>
-      <c r="Z36" s="291"/>
-      <c r="AA36" s="291"/>
-      <c r="AB36" s="291"/>
-      <c r="AC36" s="340"/>
-      <c r="AD36" s="289"/>
-      <c r="AE36" s="280" t="s">
+      <c r="U36" s="84"/>
+      <c r="V36" s="95"/>
+      <c r="W36" s="289"/>
+      <c r="X36" s="290"/>
+      <c r="Y36" s="290"/>
+      <c r="Z36" s="290"/>
+      <c r="AA36" s="290"/>
+      <c r="AB36" s="290"/>
+      <c r="AC36" s="72"/>
+      <c r="AD36" s="85"/>
+      <c r="AE36" s="73" t="s">
         <v>741</v>
       </c>
-      <c r="AF36" s="280" t="s">
+      <c r="AF36" s="73" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="37" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A37" s="270">
+    <row r="37" spans="1:32" ht="17.25">
+      <c r="A37" s="43">
         <v>36</v>
       </c>
-      <c r="B37" s="270">
+      <c r="B37" s="43">
         <v>2</v>
       </c>
-      <c r="D37" s="332"/>
-      <c r="E37" s="332"/>
-      <c r="G37" s="339" t="s">
+      <c r="D37" s="65"/>
+      <c r="G37" s="32" t="s">
         <v>584</v>
       </c>
-      <c r="H37" s="339" t="s">
+      <c r="H37" s="32" t="s">
         <v>618</v>
       </c>
-      <c r="I37" s="275">
+      <c r="I37" s="84">
         <v>8</v>
       </c>
-      <c r="J37" s="275">
-        <v>1</v>
-      </c>
-      <c r="K37" s="275" t="s">
+      <c r="J37" s="84">
+        <v>1</v>
+      </c>
+      <c r="K37" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L37" s="275" t="s">
+      <c r="L37" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M37" s="275">
-        <v>1</v>
-      </c>
-      <c r="N37" s="286">
+      <c r="M37" s="84">
+        <v>1</v>
+      </c>
+      <c r="N37" s="121">
         <v>0</v>
       </c>
-      <c r="O37" s="286"/>
-      <c r="P37" s="286"/>
-      <c r="Q37" s="286"/>
-      <c r="R37" s="286"/>
-      <c r="S37" s="286"/>
-      <c r="T37" s="288" t="s">
+      <c r="O37" s="121"/>
+      <c r="P37" s="121"/>
+      <c r="Q37" s="121"/>
+      <c r="R37" s="121"/>
+      <c r="S37" s="121"/>
+      <c r="T37" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="U37" s="275"/>
-      <c r="V37" s="336"/>
-      <c r="W37" s="290"/>
-      <c r="X37" s="291"/>
-      <c r="Y37" s="291"/>
-      <c r="Z37" s="291"/>
-      <c r="AA37" s="291"/>
-      <c r="AB37" s="291"/>
-      <c r="AC37" s="340"/>
-      <c r="AD37" s="289"/>
-      <c r="AE37" s="280" t="s">
+      <c r="U37" s="84"/>
+      <c r="V37" s="95"/>
+      <c r="W37" s="289"/>
+      <c r="X37" s="290"/>
+      <c r="Y37" s="290"/>
+      <c r="Z37" s="290"/>
+      <c r="AA37" s="290"/>
+      <c r="AB37" s="290"/>
+      <c r="AC37" s="72"/>
+      <c r="AD37" s="85"/>
+      <c r="AE37" s="73" t="s">
         <v>828</v>
       </c>
-      <c r="AF37" s="280" t="s">
+      <c r="AF37" s="73" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="38" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A38" s="270">
+    <row r="38" spans="1:32" ht="17.25">
+      <c r="A38" s="43">
         <v>37</v>
       </c>
-      <c r="B38" s="270">
+      <c r="B38" s="43">
         <v>2</v>
       </c>
-      <c r="D38" s="332"/>
-      <c r="E38" s="332"/>
-      <c r="G38" s="339" t="s">
+      <c r="D38" s="65"/>
+      <c r="G38" s="32" t="s">
         <v>632</v>
       </c>
-      <c r="H38" s="339" t="s">
+      <c r="H38" s="32" t="s">
         <v>585</v>
       </c>
-      <c r="I38" s="275">
+      <c r="I38" s="84">
         <v>9</v>
       </c>
-      <c r="J38" s="275">
-        <v>1</v>
-      </c>
-      <c r="K38" s="275" t="s">
+      <c r="J38" s="84">
+        <v>1</v>
+      </c>
+      <c r="K38" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L38" s="275" t="s">
+      <c r="L38" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M38" s="275">
-        <v>1</v>
-      </c>
-      <c r="N38" s="286">
+      <c r="M38" s="84">
+        <v>1</v>
+      </c>
+      <c r="N38" s="121">
         <v>0</v>
       </c>
-      <c r="O38" s="286"/>
-      <c r="P38" s="286"/>
-      <c r="Q38" s="286"/>
-      <c r="R38" s="286"/>
-      <c r="S38" s="286"/>
-      <c r="T38" s="288" t="s">
+      <c r="O38" s="121"/>
+      <c r="P38" s="121"/>
+      <c r="Q38" s="121"/>
+      <c r="R38" s="121"/>
+      <c r="S38" s="121"/>
+      <c r="T38" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="U38" s="275"/>
-      <c r="V38" s="336"/>
-      <c r="W38" s="290"/>
-      <c r="X38" s="291"/>
-      <c r="Y38" s="291"/>
-      <c r="Z38" s="291"/>
-      <c r="AA38" s="291"/>
-      <c r="AB38" s="291"/>
-      <c r="AC38" s="340"/>
-      <c r="AD38" s="289"/>
-      <c r="AE38" s="280" t="s">
+      <c r="U38" s="84"/>
+      <c r="V38" s="95"/>
+      <c r="W38" s="289"/>
+      <c r="X38" s="290"/>
+      <c r="Y38" s="290"/>
+      <c r="Z38" s="290"/>
+      <c r="AA38" s="290"/>
+      <c r="AB38" s="290"/>
+      <c r="AC38" s="72"/>
+      <c r="AD38" s="85"/>
+      <c r="AE38" s="73" t="s">
         <v>741</v>
       </c>
-      <c r="AF38" s="280" t="s">
+      <c r="AF38" s="73" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="39" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A39" s="270">
+    <row r="39" spans="1:32" ht="17.25">
+      <c r="A39" s="43">
         <v>38</v>
       </c>
-      <c r="B39" s="270">
+      <c r="B39" s="43">
         <v>2</v>
       </c>
-      <c r="D39" s="332"/>
-      <c r="E39" s="332"/>
-      <c r="G39" s="339" t="s">
+      <c r="D39" s="65"/>
+      <c r="G39" s="32" t="s">
         <v>586</v>
       </c>
-      <c r="H39" s="339" t="s">
+      <c r="H39" s="32" t="s">
         <v>619</v>
       </c>
-      <c r="I39" s="275">
+      <c r="I39" s="84">
         <v>10</v>
       </c>
-      <c r="J39" s="275">
-        <v>1</v>
-      </c>
-      <c r="K39" s="275" t="s">
+      <c r="J39" s="84">
+        <v>1</v>
+      </c>
+      <c r="K39" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L39" s="275" t="s">
+      <c r="L39" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M39" s="275">
-        <v>1</v>
-      </c>
-      <c r="N39" s="286">
+      <c r="M39" s="84">
+        <v>1</v>
+      </c>
+      <c r="N39" s="121">
         <v>0</v>
       </c>
-      <c r="O39" s="286"/>
-      <c r="P39" s="286"/>
-      <c r="Q39" s="286"/>
-      <c r="R39" s="286"/>
-      <c r="S39" s="286"/>
-      <c r="T39" s="288" t="s">
+      <c r="O39" s="121"/>
+      <c r="P39" s="121"/>
+      <c r="Q39" s="121"/>
+      <c r="R39" s="121"/>
+      <c r="S39" s="121"/>
+      <c r="T39" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="U39" s="275"/>
-      <c r="V39" s="336"/>
-      <c r="W39" s="290"/>
-      <c r="X39" s="291"/>
-      <c r="Y39" s="291"/>
-      <c r="Z39" s="291"/>
-      <c r="AA39" s="291"/>
-      <c r="AB39" s="291"/>
-      <c r="AC39" s="340"/>
-      <c r="AD39" s="289"/>
-      <c r="AE39" s="280" t="s">
+      <c r="U39" s="84"/>
+      <c r="V39" s="95"/>
+      <c r="W39" s="289"/>
+      <c r="X39" s="290"/>
+      <c r="Y39" s="290"/>
+      <c r="Z39" s="290"/>
+      <c r="AA39" s="290"/>
+      <c r="AB39" s="290"/>
+      <c r="AC39" s="72"/>
+      <c r="AD39" s="85"/>
+      <c r="AE39" s="73" t="s">
         <v>828</v>
       </c>
-      <c r="AF39" s="280" t="s">
+      <c r="AF39" s="73" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="40" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A40" s="270">
+    <row r="40" spans="1:32" ht="17.25">
+      <c r="A40" s="43">
         <v>39</v>
       </c>
-      <c r="B40" s="270">
+      <c r="B40" s="43">
         <v>2</v>
       </c>
-      <c r="D40" s="332"/>
-      <c r="E40" s="332"/>
-      <c r="G40" s="339" t="s">
+      <c r="D40" s="65"/>
+      <c r="G40" s="32" t="s">
         <v>633</v>
       </c>
-      <c r="H40" s="339" t="s">
+      <c r="H40" s="32" t="s">
         <v>587</v>
       </c>
-      <c r="I40" s="275">
+      <c r="I40" s="84">
         <v>11</v>
       </c>
-      <c r="J40" s="275">
-        <v>1</v>
-      </c>
-      <c r="K40" s="275" t="s">
+      <c r="J40" s="84">
+        <v>1</v>
+      </c>
+      <c r="K40" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L40" s="275" t="s">
+      <c r="L40" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M40" s="275">
-        <v>1</v>
-      </c>
-      <c r="N40" s="286">
+      <c r="M40" s="84">
+        <v>1</v>
+      </c>
+      <c r="N40" s="121">
         <v>0</v>
       </c>
-      <c r="O40" s="286"/>
-      <c r="P40" s="286"/>
-      <c r="Q40" s="286"/>
-      <c r="R40" s="286"/>
-      <c r="S40" s="286"/>
-      <c r="T40" s="288" t="s">
+      <c r="O40" s="121"/>
+      <c r="P40" s="121"/>
+      <c r="Q40" s="121"/>
+      <c r="R40" s="121"/>
+      <c r="S40" s="121"/>
+      <c r="T40" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="U40" s="275"/>
-      <c r="V40" s="336"/>
-      <c r="W40" s="290"/>
-      <c r="X40" s="291"/>
-      <c r="Y40" s="291"/>
-      <c r="Z40" s="291"/>
-      <c r="AA40" s="291"/>
-      <c r="AB40" s="291"/>
-      <c r="AC40" s="340"/>
-      <c r="AD40" s="289"/>
-      <c r="AE40" s="280" t="s">
+      <c r="U40" s="84"/>
+      <c r="V40" s="95"/>
+      <c r="W40" s="289"/>
+      <c r="X40" s="290"/>
+      <c r="Y40" s="290"/>
+      <c r="Z40" s="290"/>
+      <c r="AA40" s="290"/>
+      <c r="AB40" s="290"/>
+      <c r="AC40" s="72"/>
+      <c r="AD40" s="85"/>
+      <c r="AE40" s="73" t="s">
         <v>741</v>
       </c>
-      <c r="AF40" s="280" t="s">
+      <c r="AF40" s="73" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="41" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A41" s="270">
+    <row r="41" spans="1:32" ht="17.25">
+      <c r="A41" s="43">
         <v>40</v>
       </c>
-      <c r="B41" s="270">
+      <c r="B41" s="43">
         <v>2</v>
       </c>
-      <c r="D41" s="332"/>
-      <c r="E41" s="332"/>
-      <c r="G41" s="339" t="s">
+      <c r="D41" s="65"/>
+      <c r="G41" s="32" t="s">
         <v>634</v>
       </c>
-      <c r="H41" s="339" t="s">
+      <c r="H41" s="32" t="s">
         <v>588</v>
       </c>
-      <c r="I41" s="275">
+      <c r="I41" s="84">
         <v>12</v>
       </c>
-      <c r="J41" s="275">
-        <v>1</v>
-      </c>
-      <c r="K41" s="275" t="s">
+      <c r="J41" s="84">
+        <v>1</v>
+      </c>
+      <c r="K41" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L41" s="275" t="s">
+      <c r="L41" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M41" s="275">
-        <v>1</v>
-      </c>
-      <c r="N41" s="286">
+      <c r="M41" s="84">
+        <v>1</v>
+      </c>
+      <c r="N41" s="121">
         <v>0</v>
       </c>
-      <c r="O41" s="286"/>
-      <c r="P41" s="286"/>
-      <c r="Q41" s="286"/>
-      <c r="R41" s="286"/>
-      <c r="S41" s="286"/>
-      <c r="T41" s="288" t="s">
+      <c r="O41" s="121"/>
+      <c r="P41" s="121"/>
+      <c r="Q41" s="121"/>
+      <c r="R41" s="121"/>
+      <c r="S41" s="121"/>
+      <c r="T41" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="U41" s="275"/>
-      <c r="V41" s="336"/>
-      <c r="W41" s="290"/>
-      <c r="X41" s="291"/>
-      <c r="Y41" s="291"/>
-      <c r="Z41" s="291"/>
-      <c r="AA41" s="291"/>
-      <c r="AB41" s="291"/>
-      <c r="AC41" s="340"/>
-      <c r="AD41" s="289"/>
-      <c r="AE41" s="280" t="s">
+      <c r="U41" s="84"/>
+      <c r="V41" s="95"/>
+      <c r="W41" s="289"/>
+      <c r="X41" s="290"/>
+      <c r="Y41" s="290"/>
+      <c r="Z41" s="290"/>
+      <c r="AA41" s="290"/>
+      <c r="AB41" s="290"/>
+      <c r="AC41" s="72"/>
+      <c r="AD41" s="85"/>
+      <c r="AE41" s="73" t="s">
         <v>828</v>
       </c>
-      <c r="AF41" s="280" t="s">
+      <c r="AF41" s="73" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="42" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A42" s="270">
+    <row r="42" spans="1:32" ht="17.25">
+      <c r="A42" s="43">
         <v>41</v>
       </c>
-      <c r="B42" s="270">
+      <c r="B42" s="43">
         <v>2</v>
       </c>
-      <c r="D42" s="332"/>
-      <c r="E42" s="332"/>
-      <c r="G42" s="339" t="s">
+      <c r="D42" s="65"/>
+      <c r="G42" s="32" t="s">
         <v>635</v>
       </c>
-      <c r="H42" s="339" t="s">
+      <c r="H42" s="32" t="s">
         <v>589</v>
       </c>
-      <c r="I42" s="275">
+      <c r="I42" s="84">
         <v>13</v>
       </c>
-      <c r="J42" s="275">
-        <v>1</v>
-      </c>
-      <c r="K42" s="275" t="s">
+      <c r="J42" s="84">
+        <v>1</v>
+      </c>
+      <c r="K42" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L42" s="275" t="s">
+      <c r="L42" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M42" s="275">
-        <v>1</v>
-      </c>
-      <c r="N42" s="286">
+      <c r="M42" s="84">
+        <v>1</v>
+      </c>
+      <c r="N42" s="121">
         <v>0</v>
       </c>
-      <c r="O42" s="286"/>
-      <c r="P42" s="286"/>
-      <c r="Q42" s="286"/>
-      <c r="R42" s="286"/>
-      <c r="S42" s="286"/>
-      <c r="T42" s="288" t="s">
+      <c r="O42" s="121"/>
+      <c r="P42" s="121"/>
+      <c r="Q42" s="121"/>
+      <c r="R42" s="121"/>
+      <c r="S42" s="121"/>
+      <c r="T42" s="33" t="s">
         <v>590</v>
       </c>
-      <c r="U42" s="275"/>
-      <c r="V42" s="336"/>
-      <c r="W42" s="290"/>
-      <c r="X42" s="291"/>
-      <c r="Y42" s="291"/>
-      <c r="Z42" s="291"/>
-      <c r="AA42" s="291"/>
-      <c r="AB42" s="291"/>
-      <c r="AC42" s="340"/>
-      <c r="AD42" s="289"/>
-      <c r="AE42" s="280" t="s">
+      <c r="U42" s="84"/>
+      <c r="V42" s="95"/>
+      <c r="W42" s="289"/>
+      <c r="X42" s="290"/>
+      <c r="Y42" s="290"/>
+      <c r="Z42" s="290"/>
+      <c r="AA42" s="290"/>
+      <c r="AB42" s="290"/>
+      <c r="AC42" s="72"/>
+      <c r="AD42" s="85"/>
+      <c r="AE42" s="73" t="s">
         <v>828</v>
       </c>
-      <c r="AF42" s="280" t="s">
+      <c r="AF42" s="73" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="43" spans="1:32" s="270" customFormat="1" ht="34.5">
-      <c r="A43" s="270">
+    <row r="43" spans="1:32" ht="34.5">
+      <c r="A43" s="43">
         <v>42</v>
       </c>
-      <c r="B43" s="270">
+      <c r="B43" s="43">
         <v>2</v>
       </c>
-      <c r="D43" s="332"/>
-      <c r="E43" s="332"/>
-      <c r="G43" s="339" t="s">
+      <c r="D43" s="65"/>
+      <c r="G43" s="32" t="s">
         <v>636</v>
       </c>
-      <c r="H43" s="339" t="s">
+      <c r="H43" s="32" t="s">
         <v>591</v>
       </c>
-      <c r="I43" s="275">
+      <c r="I43" s="84">
         <v>14</v>
       </c>
-      <c r="J43" s="275">
-        <v>1</v>
-      </c>
-      <c r="K43" s="275" t="s">
+      <c r="J43" s="84">
+        <v>1</v>
+      </c>
+      <c r="K43" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L43" s="275" t="s">
+      <c r="L43" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M43" s="275">
-        <v>1</v>
-      </c>
-      <c r="N43" s="286">
+      <c r="M43" s="84">
+        <v>1</v>
+      </c>
+      <c r="N43" s="121">
         <v>0</v>
       </c>
-      <c r="O43" s="286"/>
-      <c r="P43" s="286"/>
-      <c r="Q43" s="286"/>
-      <c r="R43" s="286"/>
-      <c r="S43" s="286"/>
-      <c r="T43" s="288" t="s">
+      <c r="O43" s="121"/>
+      <c r="P43" s="121"/>
+      <c r="Q43" s="121"/>
+      <c r="R43" s="121"/>
+      <c r="S43" s="121"/>
+      <c r="T43" s="33" t="s">
         <v>592</v>
       </c>
-      <c r="U43" s="275"/>
-      <c r="V43" s="336"/>
-      <c r="W43" s="290"/>
-      <c r="X43" s="291"/>
-      <c r="Y43" s="291"/>
-      <c r="Z43" s="291"/>
-      <c r="AA43" s="291"/>
-      <c r="AB43" s="291"/>
-      <c r="AC43" s="340"/>
-      <c r="AD43" s="289"/>
-      <c r="AE43" s="280" t="s">
+      <c r="U43" s="84"/>
+      <c r="V43" s="95"/>
+      <c r="W43" s="289"/>
+      <c r="X43" s="290"/>
+      <c r="Y43" s="290"/>
+      <c r="Z43" s="290"/>
+      <c r="AA43" s="290"/>
+      <c r="AB43" s="290"/>
+      <c r="AC43" s="72"/>
+      <c r="AD43" s="85"/>
+      <c r="AE43" s="73" t="s">
         <v>828</v>
       </c>
-      <c r="AF43" s="280" t="s">
+      <c r="AF43" s="73" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="44" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A44" s="270">
+    <row r="44" spans="1:32" ht="17.25">
+      <c r="A44" s="43">
         <v>43</v>
       </c>
-      <c r="B44" s="270">
+      <c r="B44" s="43">
         <v>2</v>
       </c>
-      <c r="D44" s="332"/>
-      <c r="E44" s="332"/>
-      <c r="G44" s="339" t="s">
+      <c r="D44" s="65"/>
+      <c r="G44" s="32" t="s">
         <v>593</v>
       </c>
-      <c r="H44" s="339" t="s">
+      <c r="H44" s="32" t="s">
         <v>620</v>
       </c>
-      <c r="I44" s="275">
+      <c r="I44" s="84">
         <v>15</v>
       </c>
-      <c r="J44" s="275">
-        <v>1</v>
-      </c>
-      <c r="K44" s="275" t="s">
+      <c r="J44" s="84">
+        <v>1</v>
+      </c>
+      <c r="K44" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L44" s="275" t="s">
+      <c r="L44" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M44" s="275">
-        <v>1</v>
-      </c>
-      <c r="N44" s="286">
+      <c r="M44" s="84">
+        <v>1</v>
+      </c>
+      <c r="N44" s="121">
         <v>0</v>
       </c>
-      <c r="O44" s="286"/>
-      <c r="P44" s="286"/>
-      <c r="Q44" s="286"/>
-      <c r="R44" s="286"/>
-      <c r="S44" s="286"/>
-      <c r="T44" s="288" t="s">
+      <c r="O44" s="121"/>
+      <c r="P44" s="121"/>
+      <c r="Q44" s="121"/>
+      <c r="R44" s="121"/>
+      <c r="S44" s="121"/>
+      <c r="T44" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="U44" s="275"/>
-      <c r="V44" s="336"/>
-      <c r="W44" s="290"/>
-      <c r="X44" s="291"/>
-      <c r="Y44" s="291"/>
-      <c r="Z44" s="291"/>
-      <c r="AA44" s="291"/>
-      <c r="AB44" s="291"/>
-      <c r="AC44" s="340"/>
-      <c r="AD44" s="289"/>
-      <c r="AE44" s="280" t="s">
+      <c r="U44" s="84"/>
+      <c r="V44" s="95"/>
+      <c r="W44" s="289"/>
+      <c r="X44" s="290"/>
+      <c r="Y44" s="290"/>
+      <c r="Z44" s="290"/>
+      <c r="AA44" s="290"/>
+      <c r="AB44" s="290"/>
+      <c r="AC44" s="72"/>
+      <c r="AD44" s="85"/>
+      <c r="AE44" s="73" t="s">
         <v>828</v>
       </c>
-      <c r="AF44" s="280" t="s">
+      <c r="AF44" s="73" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="45" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A45" s="270">
+    <row r="45" spans="1:32" ht="17.25">
+      <c r="A45" s="43">
         <v>44</v>
       </c>
-      <c r="B45" s="270">
+      <c r="B45" s="43">
         <v>2</v>
       </c>
-      <c r="D45" s="332"/>
-      <c r="E45" s="332"/>
-      <c r="G45" s="339" t="s">
+      <c r="D45" s="65"/>
+      <c r="G45" s="32" t="s">
         <v>594</v>
       </c>
-      <c r="H45" s="339" t="s">
+      <c r="H45" s="32" t="s">
         <v>621</v>
       </c>
-      <c r="I45" s="275">
+      <c r="I45" s="84">
         <v>16</v>
       </c>
-      <c r="J45" s="275">
-        <v>1</v>
-      </c>
-      <c r="K45" s="275" t="s">
+      <c r="J45" s="84">
+        <v>1</v>
+      </c>
+      <c r="K45" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L45" s="275" t="s">
+      <c r="L45" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M45" s="275">
-        <v>1</v>
-      </c>
-      <c r="N45" s="286">
+      <c r="M45" s="84">
+        <v>1</v>
+      </c>
+      <c r="N45" s="121">
         <v>0</v>
       </c>
-      <c r="O45" s="286"/>
-      <c r="P45" s="286"/>
-      <c r="Q45" s="286"/>
-      <c r="R45" s="286"/>
-      <c r="S45" s="286"/>
-      <c r="T45" s="288" t="s">
+      <c r="O45" s="121"/>
+      <c r="P45" s="121"/>
+      <c r="Q45" s="121"/>
+      <c r="R45" s="121"/>
+      <c r="S45" s="121"/>
+      <c r="T45" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="U45" s="275"/>
-      <c r="V45" s="336"/>
-      <c r="W45" s="290"/>
-      <c r="X45" s="291"/>
-      <c r="Y45" s="291"/>
-      <c r="Z45" s="291"/>
-      <c r="AA45" s="291"/>
-      <c r="AB45" s="291"/>
-      <c r="AC45" s="340"/>
-      <c r="AD45" s="289"/>
-      <c r="AE45" s="280" t="s">
+      <c r="U45" s="84"/>
+      <c r="V45" s="95"/>
+      <c r="W45" s="289"/>
+      <c r="X45" s="290"/>
+      <c r="Y45" s="290"/>
+      <c r="Z45" s="290"/>
+      <c r="AA45" s="290"/>
+      <c r="AB45" s="290"/>
+      <c r="AC45" s="72"/>
+      <c r="AD45" s="85"/>
+      <c r="AE45" s="73" t="s">
         <v>828</v>
       </c>
-      <c r="AF45" s="280" t="s">
+      <c r="AF45" s="73" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="46" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A46" s="270">
+    <row r="46" spans="1:32" ht="17.25">
+      <c r="A46" s="43">
         <v>45</v>
       </c>
-      <c r="B46" s="270">
+      <c r="B46" s="43">
         <v>2</v>
       </c>
-      <c r="D46" s="332"/>
-      <c r="E46" s="332"/>
-      <c r="G46" s="339" t="s">
+      <c r="D46" s="65"/>
+      <c r="G46" s="32" t="s">
         <v>637</v>
       </c>
-      <c r="H46" s="339" t="s">
+      <c r="H46" s="32" t="s">
         <v>595</v>
       </c>
-      <c r="I46" s="275">
+      <c r="I46" s="84">
         <v>17</v>
       </c>
-      <c r="J46" s="275">
-        <v>1</v>
-      </c>
-      <c r="K46" s="275" t="s">
+      <c r="J46" s="84">
+        <v>1</v>
+      </c>
+      <c r="K46" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L46" s="275" t="s">
+      <c r="L46" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M46" s="275">
-        <v>1</v>
-      </c>
-      <c r="N46" s="286">
+      <c r="M46" s="84">
+        <v>1</v>
+      </c>
+      <c r="N46" s="121">
         <v>0</v>
       </c>
-      <c r="O46" s="286"/>
-      <c r="P46" s="286"/>
-      <c r="Q46" s="286"/>
-      <c r="R46" s="286"/>
-      <c r="S46" s="286"/>
-      <c r="T46" s="288" t="s">
+      <c r="O46" s="121"/>
+      <c r="P46" s="121"/>
+      <c r="Q46" s="121"/>
+      <c r="R46" s="121"/>
+      <c r="S46" s="121"/>
+      <c r="T46" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="U46" s="275"/>
-      <c r="V46" s="336"/>
-      <c r="W46" s="290"/>
-      <c r="X46" s="291"/>
-      <c r="Y46" s="291"/>
-      <c r="Z46" s="291"/>
-      <c r="AA46" s="291"/>
-      <c r="AB46" s="291"/>
-      <c r="AC46" s="340"/>
-      <c r="AD46" s="289"/>
-      <c r="AE46" s="280" t="s">
+      <c r="U46" s="84"/>
+      <c r="V46" s="95"/>
+      <c r="W46" s="289"/>
+      <c r="X46" s="290"/>
+      <c r="Y46" s="290"/>
+      <c r="Z46" s="290"/>
+      <c r="AA46" s="290"/>
+      <c r="AB46" s="290"/>
+      <c r="AC46" s="72"/>
+      <c r="AD46" s="85"/>
+      <c r="AE46" s="73" t="s">
         <v>827</v>
       </c>
-      <c r="AF46" s="280" t="s">
+      <c r="AF46" s="73" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="47" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A47" s="270">
+    <row r="47" spans="1:32" ht="17.25">
+      <c r="A47" s="43">
         <v>46</v>
       </c>
-      <c r="B47" s="270">
+      <c r="B47" s="43">
         <v>2</v>
       </c>
-      <c r="D47" s="332"/>
-      <c r="E47" s="332"/>
-      <c r="G47" s="339" t="s">
+      <c r="D47" s="65"/>
+      <c r="G47" s="32" t="s">
         <v>596</v>
       </c>
-      <c r="H47" s="339" t="s">
+      <c r="H47" s="32" t="s">
         <v>622</v>
       </c>
-      <c r="I47" s="275">
+      <c r="I47" s="84">
         <v>18</v>
       </c>
-      <c r="J47" s="275">
-        <v>1</v>
-      </c>
-      <c r="K47" s="275" t="s">
+      <c r="J47" s="84">
+        <v>1</v>
+      </c>
+      <c r="K47" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L47" s="275" t="s">
+      <c r="L47" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M47" s="275">
-        <v>1</v>
-      </c>
-      <c r="N47" s="286">
+      <c r="M47" s="84">
+        <v>1</v>
+      </c>
+      <c r="N47" s="121">
         <v>0</v>
       </c>
-      <c r="O47" s="286"/>
-      <c r="P47" s="286"/>
-      <c r="Q47" s="286"/>
-      <c r="R47" s="286"/>
-      <c r="S47" s="286"/>
-      <c r="T47" s="288" t="s">
+      <c r="O47" s="121"/>
+      <c r="P47" s="121"/>
+      <c r="Q47" s="121"/>
+      <c r="R47" s="121"/>
+      <c r="S47" s="121"/>
+      <c r="T47" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="U47" s="275"/>
-      <c r="V47" s="336"/>
-      <c r="W47" s="290"/>
-      <c r="X47" s="291"/>
-      <c r="Y47" s="291"/>
-      <c r="Z47" s="291"/>
-      <c r="AA47" s="291"/>
-      <c r="AB47" s="291"/>
-      <c r="AC47" s="340"/>
-      <c r="AD47" s="289"/>
-      <c r="AE47" s="280" t="s">
+      <c r="U47" s="84"/>
+      <c r="V47" s="95"/>
+      <c r="W47" s="289"/>
+      <c r="X47" s="290"/>
+      <c r="Y47" s="290"/>
+      <c r="Z47" s="290"/>
+      <c r="AA47" s="290"/>
+      <c r="AB47" s="290"/>
+      <c r="AC47" s="72"/>
+      <c r="AD47" s="85"/>
+      <c r="AE47" s="73" t="s">
         <v>827</v>
       </c>
-      <c r="AF47" s="280" t="s">
+      <c r="AF47" s="73" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="48" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A48" s="270">
+    <row r="48" spans="1:32" ht="17.25">
+      <c r="A48" s="43">
         <v>47</v>
       </c>
-      <c r="B48" s="270">
+      <c r="B48" s="43">
         <v>2</v>
       </c>
-      <c r="D48" s="332"/>
-      <c r="E48" s="332"/>
-      <c r="G48" s="339" t="s">
+      <c r="D48" s="65"/>
+      <c r="G48" s="32" t="s">
         <v>638</v>
       </c>
-      <c r="H48" s="339" t="s">
+      <c r="H48" s="32" t="s">
         <v>597</v>
       </c>
-      <c r="I48" s="275">
+      <c r="I48" s="84">
         <v>19</v>
       </c>
-      <c r="J48" s="275">
-        <v>1</v>
-      </c>
-      <c r="K48" s="275" t="s">
+      <c r="J48" s="84">
+        <v>1</v>
+      </c>
+      <c r="K48" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L48" s="275" t="s">
+      <c r="L48" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M48" s="275">
-        <v>1</v>
-      </c>
-      <c r="N48" s="286">
+      <c r="M48" s="84">
+        <v>1</v>
+      </c>
+      <c r="N48" s="121">
         <v>0</v>
       </c>
-      <c r="O48" s="286"/>
-      <c r="P48" s="286"/>
-      <c r="Q48" s="286"/>
-      <c r="R48" s="286"/>
-      <c r="S48" s="286"/>
-      <c r="T48" s="288" t="s">
+      <c r="O48" s="121"/>
+      <c r="P48" s="121"/>
+      <c r="Q48" s="121"/>
+      <c r="R48" s="121"/>
+      <c r="S48" s="121"/>
+      <c r="T48" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="U48" s="275"/>
-      <c r="V48" s="336"/>
-      <c r="W48" s="290"/>
-      <c r="X48" s="291"/>
-      <c r="Y48" s="291"/>
-      <c r="Z48" s="291"/>
-      <c r="AA48" s="291"/>
-      <c r="AB48" s="291"/>
-      <c r="AC48" s="340"/>
-      <c r="AD48" s="289"/>
-      <c r="AE48" s="280" t="s">
+      <c r="U48" s="84"/>
+      <c r="V48" s="95"/>
+      <c r="W48" s="289"/>
+      <c r="X48" s="290"/>
+      <c r="Y48" s="290"/>
+      <c r="Z48" s="290"/>
+      <c r="AA48" s="290"/>
+      <c r="AB48" s="290"/>
+      <c r="AC48" s="72"/>
+      <c r="AD48" s="85"/>
+      <c r="AE48" s="73" t="s">
         <v>827</v>
       </c>
-      <c r="AF48" s="280" t="s">
+      <c r="AF48" s="73" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="49" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A49" s="270">
+    <row r="49" spans="1:32" ht="17.25">
+      <c r="A49" s="43">
         <v>48</v>
       </c>
-      <c r="B49" s="270">
+      <c r="B49" s="43">
         <v>2</v>
       </c>
-      <c r="D49" s="332"/>
-      <c r="E49" s="332"/>
-      <c r="G49" s="339" t="s">
+      <c r="D49" s="65"/>
+      <c r="G49" s="32" t="s">
         <v>598</v>
       </c>
-      <c r="H49" s="339" t="s">
+      <c r="H49" s="32" t="s">
         <v>623</v>
       </c>
-      <c r="I49" s="275">
+      <c r="I49" s="84">
         <v>20</v>
       </c>
-      <c r="J49" s="275">
-        <v>1</v>
-      </c>
-      <c r="K49" s="275" t="s">
+      <c r="J49" s="84">
+        <v>1</v>
+      </c>
+      <c r="K49" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L49" s="275" t="s">
+      <c r="L49" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M49" s="275">
-        <v>1</v>
-      </c>
-      <c r="N49" s="286">
+      <c r="M49" s="84">
+        <v>1</v>
+      </c>
+      <c r="N49" s="121">
         <v>0</v>
       </c>
-      <c r="O49" s="286"/>
-      <c r="P49" s="286"/>
-      <c r="Q49" s="286"/>
-      <c r="R49" s="286"/>
-      <c r="S49" s="286"/>
-      <c r="T49" s="288" t="s">
+      <c r="O49" s="121"/>
+      <c r="P49" s="121"/>
+      <c r="Q49" s="121"/>
+      <c r="R49" s="121"/>
+      <c r="S49" s="121"/>
+      <c r="T49" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="U49" s="275"/>
-      <c r="V49" s="336"/>
-      <c r="W49" s="290"/>
-      <c r="X49" s="291"/>
-      <c r="Y49" s="291"/>
-      <c r="Z49" s="291"/>
-      <c r="AA49" s="291"/>
-      <c r="AB49" s="291"/>
-      <c r="AC49" s="340"/>
-      <c r="AD49" s="289"/>
-      <c r="AE49" s="280" t="s">
+      <c r="U49" s="84"/>
+      <c r="V49" s="95"/>
+      <c r="W49" s="289"/>
+      <c r="X49" s="290"/>
+      <c r="Y49" s="290"/>
+      <c r="Z49" s="290"/>
+      <c r="AA49" s="290"/>
+      <c r="AB49" s="290"/>
+      <c r="AC49" s="72"/>
+      <c r="AD49" s="85"/>
+      <c r="AE49" s="73" t="s">
         <v>827</v>
       </c>
-      <c r="AF49" s="280" t="s">
+      <c r="AF49" s="73" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="50" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A50" s="270">
+    <row r="50" spans="1:32" ht="17.25">
+      <c r="A50" s="43">
         <v>49</v>
       </c>
-      <c r="B50" s="270">
+      <c r="B50" s="43">
         <v>2</v>
       </c>
-      <c r="D50" s="332"/>
-      <c r="E50" s="332"/>
-      <c r="G50" s="339" t="s">
+      <c r="D50" s="65"/>
+      <c r="G50" s="32" t="s">
         <v>599</v>
       </c>
-      <c r="H50" s="339" t="s">
+      <c r="H50" s="32" t="s">
         <v>624</v>
       </c>
-      <c r="I50" s="275">
+      <c r="I50" s="84">
         <v>21</v>
       </c>
-      <c r="J50" s="275">
-        <v>1</v>
-      </c>
-      <c r="K50" s="275" t="s">
+      <c r="J50" s="84">
+        <v>1</v>
+      </c>
+      <c r="K50" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L50" s="275" t="s">
+      <c r="L50" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M50" s="275">
-        <v>1</v>
-      </c>
-      <c r="N50" s="286">
+      <c r="M50" s="84">
+        <v>1</v>
+      </c>
+      <c r="N50" s="121">
         <v>0</v>
       </c>
-      <c r="O50" s="286"/>
-      <c r="P50" s="286"/>
-      <c r="Q50" s="286"/>
-      <c r="R50" s="286"/>
-      <c r="S50" s="286"/>
-      <c r="T50" s="288" t="s">
+      <c r="O50" s="121"/>
+      <c r="P50" s="121"/>
+      <c r="Q50" s="121"/>
+      <c r="R50" s="121"/>
+      <c r="S50" s="121"/>
+      <c r="T50" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="U50" s="275"/>
-      <c r="V50" s="336"/>
-      <c r="W50" s="290"/>
-      <c r="X50" s="291"/>
-      <c r="Y50" s="291"/>
-      <c r="Z50" s="291"/>
-      <c r="AA50" s="291"/>
-      <c r="AB50" s="291"/>
-      <c r="AC50" s="340"/>
-      <c r="AD50" s="289"/>
-      <c r="AE50" s="280" t="s">
+      <c r="U50" s="84"/>
+      <c r="V50" s="95"/>
+      <c r="W50" s="289"/>
+      <c r="X50" s="290"/>
+      <c r="Y50" s="290"/>
+      <c r="Z50" s="290"/>
+      <c r="AA50" s="290"/>
+      <c r="AB50" s="290"/>
+      <c r="AC50" s="72"/>
+      <c r="AD50" s="85"/>
+      <c r="AE50" s="73" t="s">
         <v>827</v>
       </c>
-      <c r="AF50" s="280" t="s">
+      <c r="AF50" s="73" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="51" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A51" s="270">
+    <row r="51" spans="1:32" ht="17.25">
+      <c r="A51" s="43">
         <v>50</v>
       </c>
-      <c r="B51" s="270">
+      <c r="B51" s="43">
         <v>2</v>
       </c>
-      <c r="D51" s="332"/>
-      <c r="E51" s="332"/>
-      <c r="G51" s="339" t="s">
+      <c r="D51" s="65"/>
+      <c r="G51" s="32" t="s">
         <v>639</v>
       </c>
-      <c r="H51" s="339" t="s">
+      <c r="H51" s="32" t="s">
         <v>600</v>
       </c>
-      <c r="I51" s="275">
+      <c r="I51" s="84">
         <v>22</v>
       </c>
-      <c r="J51" s="275">
-        <v>1</v>
-      </c>
-      <c r="K51" s="275" t="s">
+      <c r="J51" s="84">
+        <v>1</v>
+      </c>
+      <c r="K51" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L51" s="275" t="s">
+      <c r="L51" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M51" s="275">
-        <v>1</v>
-      </c>
-      <c r="N51" s="286">
+      <c r="M51" s="84">
+        <v>1</v>
+      </c>
+      <c r="N51" s="121">
         <v>0</v>
       </c>
-      <c r="O51" s="286"/>
-      <c r="P51" s="286"/>
-      <c r="Q51" s="286"/>
-      <c r="R51" s="286"/>
-      <c r="S51" s="286"/>
-      <c r="T51" s="288" t="s">
+      <c r="O51" s="121"/>
+      <c r="P51" s="121"/>
+      <c r="Q51" s="121"/>
+      <c r="R51" s="121"/>
+      <c r="S51" s="121"/>
+      <c r="T51" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="U51" s="275"/>
-      <c r="V51" s="336"/>
-      <c r="W51" s="290"/>
-      <c r="X51" s="291"/>
-      <c r="Y51" s="291"/>
-      <c r="Z51" s="291"/>
-      <c r="AA51" s="291"/>
-      <c r="AB51" s="291"/>
-      <c r="AC51" s="340"/>
-      <c r="AD51" s="289"/>
-      <c r="AE51" s="280" t="s">
+      <c r="U51" s="84"/>
+      <c r="V51" s="95"/>
+      <c r="W51" s="289"/>
+      <c r="X51" s="290"/>
+      <c r="Y51" s="290"/>
+      <c r="Z51" s="290"/>
+      <c r="AA51" s="290"/>
+      <c r="AB51" s="290"/>
+      <c r="AC51" s="72"/>
+      <c r="AD51" s="85"/>
+      <c r="AE51" s="73" t="s">
         <v>827</v>
       </c>
-      <c r="AF51" s="280" t="s">
+      <c r="AF51" s="73" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="52" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A52" s="270">
+    <row r="52" spans="1:32" ht="17.25">
+      <c r="A52" s="43">
         <v>51</v>
       </c>
-      <c r="B52" s="270">
+      <c r="B52" s="43">
         <v>2</v>
       </c>
-      <c r="D52" s="332"/>
-      <c r="E52" s="332"/>
-      <c r="G52" s="339" t="s">
+      <c r="D52" s="65"/>
+      <c r="G52" s="32" t="s">
         <v>640</v>
       </c>
-      <c r="H52" s="339" t="s">
+      <c r="H52" s="32" t="s">
         <v>601</v>
       </c>
-      <c r="I52" s="275">
+      <c r="I52" s="84">
         <v>23</v>
       </c>
-      <c r="J52" s="275">
-        <v>1</v>
-      </c>
-      <c r="K52" s="275" t="s">
+      <c r="J52" s="84">
+        <v>1</v>
+      </c>
+      <c r="K52" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L52" s="275" t="s">
+      <c r="L52" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M52" s="275">
-        <v>1</v>
-      </c>
-      <c r="N52" s="286">
+      <c r="M52" s="84">
+        <v>1</v>
+      </c>
+      <c r="N52" s="121">
         <v>0</v>
       </c>
-      <c r="O52" s="286"/>
-      <c r="P52" s="286"/>
-      <c r="Q52" s="286"/>
-      <c r="R52" s="286"/>
-      <c r="S52" s="286"/>
-      <c r="T52" s="288" t="s">
+      <c r="O52" s="121"/>
+      <c r="P52" s="121"/>
+      <c r="Q52" s="121"/>
+      <c r="R52" s="121"/>
+      <c r="S52" s="121"/>
+      <c r="T52" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="U52" s="275"/>
-      <c r="V52" s="336"/>
-      <c r="W52" s="290"/>
-      <c r="X52" s="291"/>
-      <c r="Y52" s="291"/>
-      <c r="Z52" s="291"/>
-      <c r="AA52" s="291"/>
-      <c r="AB52" s="291"/>
-      <c r="AC52" s="340"/>
-      <c r="AD52" s="289"/>
-      <c r="AE52" s="280" t="s">
+      <c r="U52" s="84"/>
+      <c r="V52" s="95"/>
+      <c r="W52" s="289"/>
+      <c r="X52" s="290"/>
+      <c r="Y52" s="290"/>
+      <c r="Z52" s="290"/>
+      <c r="AA52" s="290"/>
+      <c r="AB52" s="290"/>
+      <c r="AC52" s="72"/>
+      <c r="AD52" s="85"/>
+      <c r="AE52" s="73" t="s">
         <v>827</v>
       </c>
-      <c r="AF52" s="280" t="s">
+      <c r="AF52" s="73" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="53" spans="1:32" s="270" customFormat="1" ht="34.5">
-      <c r="A53" s="270">
+    <row r="53" spans="1:32" ht="34.5">
+      <c r="A53" s="43">
         <v>52</v>
       </c>
-      <c r="B53" s="270">
+      <c r="B53" s="43">
         <v>2</v>
       </c>
-      <c r="D53" s="332"/>
-      <c r="E53" s="332"/>
-      <c r="G53" s="339" t="s">
+      <c r="D53" s="65"/>
+      <c r="G53" s="32" t="s">
         <v>641</v>
       </c>
-      <c r="H53" s="339" t="s">
+      <c r="H53" s="32" t="s">
         <v>602</v>
       </c>
-      <c r="I53" s="275">
+      <c r="I53" s="84">
         <v>24</v>
       </c>
-      <c r="J53" s="275">
-        <v>1</v>
-      </c>
-      <c r="K53" s="275" t="s">
+      <c r="J53" s="84">
+        <v>1</v>
+      </c>
+      <c r="K53" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L53" s="275" t="s">
+      <c r="L53" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M53" s="275">
-        <v>1</v>
-      </c>
-      <c r="N53" s="286">
+      <c r="M53" s="84">
+        <v>1</v>
+      </c>
+      <c r="N53" s="121">
         <v>0</v>
       </c>
-      <c r="O53" s="286"/>
-      <c r="P53" s="286"/>
-      <c r="Q53" s="286"/>
-      <c r="R53" s="286"/>
-      <c r="S53" s="286"/>
-      <c r="T53" s="288" t="s">
+      <c r="O53" s="121"/>
+      <c r="P53" s="121"/>
+      <c r="Q53" s="121"/>
+      <c r="R53" s="121"/>
+      <c r="S53" s="121"/>
+      <c r="T53" s="33" t="s">
         <v>603</v>
       </c>
-      <c r="U53" s="275"/>
-      <c r="V53" s="336"/>
-      <c r="W53" s="290"/>
-      <c r="X53" s="291"/>
-      <c r="Y53" s="291"/>
-      <c r="Z53" s="291"/>
-      <c r="AA53" s="291"/>
-      <c r="AB53" s="291"/>
-      <c r="AC53" s="340"/>
-      <c r="AD53" s="289"/>
-      <c r="AE53" s="280" t="s">
+      <c r="U53" s="84"/>
+      <c r="V53" s="95"/>
+      <c r="W53" s="289"/>
+      <c r="X53" s="290"/>
+      <c r="Y53" s="290"/>
+      <c r="Z53" s="290"/>
+      <c r="AA53" s="290"/>
+      <c r="AB53" s="290"/>
+      <c r="AC53" s="72"/>
+      <c r="AD53" s="85"/>
+      <c r="AE53" s="73" t="s">
         <v>827</v>
       </c>
-      <c r="AF53" s="280" t="s">
+      <c r="AF53" s="73" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="54" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A54" s="270">
+    <row r="54" spans="1:32" ht="17.25">
+      <c r="A54" s="43">
         <v>53</v>
       </c>
-      <c r="B54" s="270">
+      <c r="B54" s="43">
         <v>2</v>
       </c>
-      <c r="D54" s="332"/>
-      <c r="E54" s="332"/>
-      <c r="G54" s="339" t="s">
+      <c r="D54" s="65"/>
+      <c r="G54" s="32" t="s">
         <v>604</v>
       </c>
-      <c r="H54" s="339" t="s">
+      <c r="H54" s="32" t="s">
         <v>625</v>
       </c>
-      <c r="I54" s="275">
+      <c r="I54" s="84">
         <v>25</v>
       </c>
-      <c r="J54" s="275">
-        <v>1</v>
-      </c>
-      <c r="K54" s="275" t="s">
+      <c r="J54" s="84">
+        <v>1</v>
+      </c>
+      <c r="K54" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L54" s="275" t="s">
+      <c r="L54" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M54" s="275">
-        <v>1</v>
-      </c>
-      <c r="N54" s="286">
+      <c r="M54" s="84">
+        <v>1</v>
+      </c>
+      <c r="N54" s="121">
         <v>0</v>
       </c>
-      <c r="O54" s="286"/>
-      <c r="P54" s="286"/>
-      <c r="Q54" s="286"/>
-      <c r="R54" s="286"/>
-      <c r="S54" s="286"/>
-      <c r="T54" s="288" t="s">
+      <c r="O54" s="121"/>
+      <c r="P54" s="121"/>
+      <c r="Q54" s="121"/>
+      <c r="R54" s="121"/>
+      <c r="S54" s="121"/>
+      <c r="T54" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="U54" s="275"/>
-      <c r="V54" s="336"/>
-      <c r="W54" s="290"/>
-      <c r="X54" s="291"/>
-      <c r="Y54" s="291"/>
-      <c r="Z54" s="291"/>
-      <c r="AA54" s="291"/>
-      <c r="AB54" s="291"/>
-      <c r="AC54" s="340"/>
-      <c r="AD54" s="289"/>
-      <c r="AE54" s="280" t="s">
+      <c r="U54" s="84"/>
+      <c r="V54" s="95"/>
+      <c r="W54" s="289"/>
+      <c r="X54" s="290"/>
+      <c r="Y54" s="290"/>
+      <c r="Z54" s="290"/>
+      <c r="AA54" s="290"/>
+      <c r="AB54" s="290"/>
+      <c r="AC54" s="72"/>
+      <c r="AD54" s="85"/>
+      <c r="AE54" s="73" t="s">
         <v>827</v>
       </c>
-      <c r="AF54" s="280" t="s">
+      <c r="AF54" s="73" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="55" spans="1:32" s="270" customFormat="1" ht="34.5">
-      <c r="A55" s="270">
+    <row r="55" spans="1:32" ht="34.5">
+      <c r="A55" s="43">
         <v>54</v>
       </c>
-      <c r="B55" s="270">
+      <c r="B55" s="43">
         <v>2</v>
       </c>
-      <c r="D55" s="332"/>
-      <c r="E55" s="332"/>
-      <c r="G55" s="339" t="s">
+      <c r="D55" s="65"/>
+      <c r="G55" s="32" t="s">
         <v>644</v>
       </c>
-      <c r="H55" s="339" t="s">
+      <c r="H55" s="32" t="s">
         <v>605</v>
       </c>
-      <c r="I55" s="275">
+      <c r="I55" s="84">
         <v>26</v>
       </c>
-      <c r="J55" s="275">
-        <v>1</v>
-      </c>
-      <c r="K55" s="275" t="s">
+      <c r="J55" s="84">
+        <v>1</v>
+      </c>
+      <c r="K55" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L55" s="275" t="s">
+      <c r="L55" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M55" s="275">
-        <v>1</v>
-      </c>
-      <c r="N55" s="286">
+      <c r="M55" s="84">
+        <v>1</v>
+      </c>
+      <c r="N55" s="121">
         <v>0</v>
       </c>
-      <c r="O55" s="286"/>
-      <c r="P55" s="286"/>
-      <c r="Q55" s="286"/>
-      <c r="R55" s="286"/>
-      <c r="S55" s="286"/>
-      <c r="T55" s="288" t="s">
+      <c r="O55" s="121"/>
+      <c r="P55" s="121"/>
+      <c r="Q55" s="121"/>
+      <c r="R55" s="121"/>
+      <c r="S55" s="121"/>
+      <c r="T55" s="33" t="s">
         <v>606</v>
       </c>
-      <c r="U55" s="275"/>
-      <c r="V55" s="336"/>
-      <c r="W55" s="290"/>
-      <c r="X55" s="291"/>
-      <c r="Y55" s="291"/>
-      <c r="Z55" s="291"/>
-      <c r="AA55" s="291"/>
-      <c r="AB55" s="291"/>
-      <c r="AC55" s="340"/>
-      <c r="AD55" s="289"/>
-      <c r="AE55" s="280" t="s">
+      <c r="U55" s="84"/>
+      <c r="V55" s="95"/>
+      <c r="W55" s="289"/>
+      <c r="X55" s="290"/>
+      <c r="Y55" s="290"/>
+      <c r="Z55" s="290"/>
+      <c r="AA55" s="290"/>
+      <c r="AB55" s="290"/>
+      <c r="AC55" s="72"/>
+      <c r="AD55" s="85"/>
+      <c r="AE55" s="73" t="s">
         <v>827</v>
       </c>
-      <c r="AF55" s="280" t="s">
+      <c r="AF55" s="73" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="56" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A56" s="270">
+    <row r="56" spans="1:32" ht="17.25">
+      <c r="A56" s="43">
         <v>55</v>
       </c>
-      <c r="B56" s="270">
+      <c r="B56" s="43">
         <v>2</v>
       </c>
-      <c r="D56" s="332"/>
-      <c r="E56" s="332"/>
-      <c r="G56" s="339" t="s">
+      <c r="D56" s="65"/>
+      <c r="G56" s="32" t="s">
         <v>645</v>
       </c>
-      <c r="H56" s="339" t="s">
+      <c r="H56" s="32" t="s">
         <v>607</v>
       </c>
-      <c r="I56" s="275">
+      <c r="I56" s="84">
         <v>27</v>
       </c>
-      <c r="J56" s="275">
-        <v>1</v>
-      </c>
-      <c r="K56" s="275" t="s">
+      <c r="J56" s="84">
+        <v>1</v>
+      </c>
+      <c r="K56" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L56" s="275" t="s">
+      <c r="L56" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M56" s="275">
-        <v>1</v>
-      </c>
-      <c r="N56" s="286">
+      <c r="M56" s="84">
+        <v>1</v>
+      </c>
+      <c r="N56" s="121">
         <v>0</v>
       </c>
-      <c r="O56" s="286"/>
-      <c r="P56" s="286"/>
-      <c r="Q56" s="286"/>
-      <c r="R56" s="286"/>
-      <c r="S56" s="286"/>
-      <c r="T56" s="288" t="s">
+      <c r="O56" s="121"/>
+      <c r="P56" s="121"/>
+      <c r="Q56" s="121"/>
+      <c r="R56" s="121"/>
+      <c r="S56" s="121"/>
+      <c r="T56" s="33" t="s">
         <v>590</v>
       </c>
-      <c r="U56" s="275"/>
-      <c r="V56" s="336"/>
-      <c r="W56" s="290"/>
-      <c r="X56" s="291"/>
-      <c r="Y56" s="291"/>
-      <c r="Z56" s="291"/>
-      <c r="AA56" s="291"/>
-      <c r="AB56" s="291"/>
-      <c r="AC56" s="340"/>
-      <c r="AD56" s="289"/>
-      <c r="AE56" s="280" t="s">
+      <c r="U56" s="84"/>
+      <c r="V56" s="95"/>
+      <c r="W56" s="289"/>
+      <c r="X56" s="290"/>
+      <c r="Y56" s="290"/>
+      <c r="Z56" s="290"/>
+      <c r="AA56" s="290"/>
+      <c r="AB56" s="290"/>
+      <c r="AC56" s="72"/>
+      <c r="AD56" s="85"/>
+      <c r="AE56" s="73" t="s">
         <v>827</v>
       </c>
-      <c r="AF56" s="280" t="s">
+      <c r="AF56" s="73" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="57" spans="1:32" s="270" customFormat="1" ht="34.5">
-      <c r="A57" s="270">
+    <row r="57" spans="1:32" ht="34.5">
+      <c r="A57" s="43">
         <v>56</v>
       </c>
-      <c r="B57" s="270">
+      <c r="B57" s="43">
         <v>2</v>
       </c>
-      <c r="D57" s="332"/>
-      <c r="E57" s="332"/>
-      <c r="G57" s="339" t="s">
+      <c r="D57" s="65"/>
+      <c r="G57" s="32" t="s">
         <v>642</v>
       </c>
-      <c r="H57" s="339" t="s">
+      <c r="H57" s="32" t="s">
         <v>608</v>
       </c>
-      <c r="I57" s="275">
+      <c r="I57" s="84">
         <v>28</v>
       </c>
-      <c r="J57" s="275">
-        <v>1</v>
-      </c>
-      <c r="K57" s="275" t="s">
+      <c r="J57" s="84">
+        <v>1</v>
+      </c>
+      <c r="K57" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L57" s="275" t="s">
+      <c r="L57" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M57" s="275">
-        <v>1</v>
-      </c>
-      <c r="N57" s="286">
+      <c r="M57" s="84">
+        <v>1</v>
+      </c>
+      <c r="N57" s="121">
         <v>0</v>
       </c>
-      <c r="O57" s="286"/>
-      <c r="P57" s="286"/>
-      <c r="Q57" s="286"/>
-      <c r="R57" s="286"/>
-      <c r="S57" s="286"/>
-      <c r="T57" s="288" t="s">
+      <c r="O57" s="121"/>
+      <c r="P57" s="121"/>
+      <c r="Q57" s="121"/>
+      <c r="R57" s="121"/>
+      <c r="S57" s="121"/>
+      <c r="T57" s="33" t="s">
         <v>609</v>
       </c>
-      <c r="U57" s="275"/>
-      <c r="V57" s="336"/>
-      <c r="W57" s="290"/>
-      <c r="X57" s="291"/>
-      <c r="Y57" s="291"/>
-      <c r="Z57" s="291"/>
-      <c r="AA57" s="291"/>
-      <c r="AB57" s="291"/>
-      <c r="AC57" s="340"/>
-      <c r="AD57" s="289"/>
-      <c r="AE57" s="280" t="s">
+      <c r="U57" s="84"/>
+      <c r="V57" s="95"/>
+      <c r="W57" s="289"/>
+      <c r="X57" s="290"/>
+      <c r="Y57" s="290"/>
+      <c r="Z57" s="290"/>
+      <c r="AA57" s="290"/>
+      <c r="AB57" s="290"/>
+      <c r="AC57" s="72"/>
+      <c r="AD57" s="85"/>
+      <c r="AE57" s="73" t="s">
         <v>827</v>
       </c>
-      <c r="AF57" s="280" t="s">
+      <c r="AF57" s="73" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="58" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A58" s="270">
+    <row r="58" spans="1:32" ht="17.25">
+      <c r="A58" s="43">
         <v>57</v>
       </c>
-      <c r="B58" s="270">
+      <c r="B58" s="43">
         <v>2</v>
       </c>
-      <c r="D58" s="332"/>
-      <c r="E58" s="332"/>
-      <c r="G58" s="339" t="s">
+      <c r="D58" s="65"/>
+      <c r="G58" s="32" t="s">
         <v>643</v>
       </c>
-      <c r="H58" s="339" t="s">
+      <c r="H58" s="32" t="s">
         <v>610</v>
       </c>
-      <c r="I58" s="275">
+      <c r="I58" s="84">
         <v>29</v>
       </c>
-      <c r="J58" s="275">
-        <v>1</v>
-      </c>
-      <c r="K58" s="275" t="s">
+      <c r="J58" s="84">
+        <v>1</v>
+      </c>
+      <c r="K58" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L58" s="275" t="s">
+      <c r="L58" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M58" s="275">
-        <v>1</v>
-      </c>
-      <c r="N58" s="286">
+      <c r="M58" s="84">
+        <v>1</v>
+      </c>
+      <c r="N58" s="121">
         <v>0</v>
       </c>
-      <c r="O58" s="286"/>
-      <c r="P58" s="286"/>
-      <c r="Q58" s="286"/>
-      <c r="R58" s="286"/>
-      <c r="S58" s="286"/>
-      <c r="T58" s="288" t="s">
+      <c r="O58" s="121"/>
+      <c r="P58" s="121"/>
+      <c r="Q58" s="121"/>
+      <c r="R58" s="121"/>
+      <c r="S58" s="121"/>
+      <c r="T58" s="33" t="s">
         <v>590</v>
       </c>
-      <c r="U58" s="275"/>
-      <c r="V58" s="336"/>
-      <c r="W58" s="290"/>
-      <c r="X58" s="291"/>
-      <c r="Y58" s="291"/>
-      <c r="Z58" s="291"/>
-      <c r="AA58" s="291"/>
-      <c r="AB58" s="291"/>
-      <c r="AC58" s="340"/>
-      <c r="AD58" s="289"/>
-      <c r="AE58" s="280" t="s">
+      <c r="U58" s="84"/>
+      <c r="V58" s="95"/>
+      <c r="W58" s="289"/>
+      <c r="X58" s="290"/>
+      <c r="Y58" s="290"/>
+      <c r="Z58" s="290"/>
+      <c r="AA58" s="290"/>
+      <c r="AB58" s="290"/>
+      <c r="AC58" s="72"/>
+      <c r="AD58" s="85"/>
+      <c r="AE58" s="73" t="s">
         <v>827</v>
       </c>
-      <c r="AF58" s="280" t="s">
+      <c r="AF58" s="73" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="59" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A59" s="270">
+    <row r="59" spans="1:32" ht="17.25">
+      <c r="A59" s="43">
         <v>58</v>
       </c>
-      <c r="B59" s="270">
+      <c r="B59" s="43">
         <v>2</v>
       </c>
-      <c r="D59" s="332"/>
-      <c r="E59" s="332"/>
-      <c r="G59" s="339" t="s">
+      <c r="D59" s="65"/>
+      <c r="G59" s="32" t="s">
         <v>646</v>
       </c>
-      <c r="H59" s="339" t="s">
+      <c r="H59" s="32" t="s">
         <v>611</v>
       </c>
-      <c r="I59" s="275">
+      <c r="I59" s="84">
         <v>30</v>
       </c>
-      <c r="J59" s="275">
-        <v>1</v>
-      </c>
-      <c r="K59" s="275" t="s">
+      <c r="J59" s="84">
+        <v>1</v>
+      </c>
+      <c r="K59" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L59" s="275" t="s">
+      <c r="L59" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M59" s="275">
-        <v>1</v>
-      </c>
-      <c r="N59" s="286">
+      <c r="M59" s="84">
+        <v>1</v>
+      </c>
+      <c r="N59" s="121">
         <v>0</v>
       </c>
-      <c r="O59" s="286"/>
-      <c r="P59" s="286"/>
-      <c r="Q59" s="286"/>
-      <c r="R59" s="286"/>
-      <c r="S59" s="286"/>
-      <c r="T59" s="288" t="s">
+      <c r="O59" s="121"/>
+      <c r="P59" s="121"/>
+      <c r="Q59" s="121"/>
+      <c r="R59" s="121"/>
+      <c r="S59" s="121"/>
+      <c r="T59" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="U59" s="275"/>
-      <c r="V59" s="336"/>
-      <c r="W59" s="290"/>
-      <c r="X59" s="291"/>
-      <c r="Y59" s="291"/>
-      <c r="Z59" s="291"/>
-      <c r="AA59" s="291"/>
-      <c r="AB59" s="291"/>
-      <c r="AC59" s="340"/>
-      <c r="AD59" s="289"/>
-      <c r="AE59" s="280" t="s">
+      <c r="U59" s="84"/>
+      <c r="V59" s="95"/>
+      <c r="W59" s="289"/>
+      <c r="X59" s="290"/>
+      <c r="Y59" s="290"/>
+      <c r="Z59" s="290"/>
+      <c r="AA59" s="290"/>
+      <c r="AB59" s="290"/>
+      <c r="AC59" s="72"/>
+      <c r="AD59" s="85"/>
+      <c r="AE59" s="73" t="s">
         <v>827</v>
       </c>
-      <c r="AF59" s="280" t="s">
+      <c r="AF59" s="73" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="60" spans="1:32" s="270" customFormat="1" ht="17.25">
-      <c r="A60" s="270">
+    <row r="60" spans="1:32" ht="17.25">
+      <c r="A60" s="43">
         <v>59</v>
       </c>
-      <c r="B60" s="270">
+      <c r="B60" s="43">
         <v>2</v>
       </c>
-      <c r="D60" s="332"/>
-      <c r="E60" s="332"/>
-      <c r="G60" s="339" t="s">
+      <c r="D60" s="65"/>
+      <c r="G60" s="32" t="s">
         <v>612</v>
       </c>
-      <c r="H60" s="339" t="s">
+      <c r="H60" s="32" t="s">
         <v>626</v>
       </c>
-      <c r="I60" s="275">
+      <c r="I60" s="84">
         <v>31</v>
       </c>
-      <c r="J60" s="275">
-        <v>1</v>
-      </c>
-      <c r="K60" s="275" t="s">
+      <c r="J60" s="84">
+        <v>1</v>
+      </c>
+      <c r="K60" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L60" s="275" t="s">
+      <c r="L60" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M60" s="275">
-        <v>1</v>
-      </c>
-      <c r="N60" s="286">
+      <c r="M60" s="84">
+        <v>1</v>
+      </c>
+      <c r="N60" s="121">
         <v>0</v>
       </c>
-      <c r="O60" s="286"/>
-      <c r="P60" s="286"/>
-      <c r="Q60" s="286"/>
-      <c r="R60" s="286"/>
-      <c r="S60" s="286"/>
-      <c r="T60" s="288" t="s">
+      <c r="O60" s="121"/>
+      <c r="P60" s="121"/>
+      <c r="Q60" s="121"/>
+      <c r="R60" s="121"/>
+      <c r="S60" s="121"/>
+      <c r="T60" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="U60" s="275"/>
-      <c r="V60" s="336"/>
-      <c r="W60" s="290"/>
-      <c r="X60" s="291"/>
-      <c r="Y60" s="291"/>
-      <c r="Z60" s="291"/>
-      <c r="AA60" s="291"/>
-      <c r="AB60" s="291"/>
-      <c r="AC60" s="340"/>
-      <c r="AD60" s="289"/>
-      <c r="AE60" s="280" t="s">
+      <c r="U60" s="84"/>
+      <c r="V60" s="95"/>
+      <c r="W60" s="289"/>
+      <c r="X60" s="290"/>
+      <c r="Y60" s="290"/>
+      <c r="Z60" s="290"/>
+      <c r="AA60" s="290"/>
+      <c r="AB60" s="290"/>
+      <c r="AC60" s="72"/>
+      <c r="AD60" s="85"/>
+      <c r="AE60" s="73" t="s">
         <v>827</v>
       </c>
-      <c r="AF60" s="280" t="s">
+      <c r="AF60" s="73" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="61" spans="1:32" s="270" customFormat="1" ht="69">
-      <c r="A61" s="270">
+    <row r="61" spans="1:32" ht="69">
+      <c r="A61" s="43">
         <v>60</v>
       </c>
-      <c r="B61" s="270">
+      <c r="B61" s="43">
         <v>2</v>
       </c>
-      <c r="D61" s="332"/>
-      <c r="E61" s="332"/>
-      <c r="G61" s="339" t="s">
+      <c r="D61" s="65"/>
+      <c r="G61" s="32" t="s">
         <v>647</v>
       </c>
-      <c r="H61" s="339" t="s">
+      <c r="H61" s="32" t="s">
         <v>613</v>
       </c>
-      <c r="I61" s="275">
+      <c r="I61" s="84">
         <v>32</v>
       </c>
-      <c r="J61" s="275">
+      <c r="J61" s="84">
         <v>8</v>
       </c>
-      <c r="K61" s="275" t="s">
+      <c r="K61" s="84" t="s">
         <v>467</v>
       </c>
-      <c r="L61" s="275" t="s">
+      <c r="L61" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="M61" s="275">
-        <v>1</v>
-      </c>
-      <c r="N61" s="286">
+      <c r="M61" s="84">
+        <v>1</v>
+      </c>
+      <c r="N61" s="121">
         <v>0</v>
       </c>
-      <c r="O61" s="286"/>
-      <c r="P61" s="286"/>
-      <c r="Q61" s="286"/>
-      <c r="R61" s="286"/>
-      <c r="S61" s="286"/>
-      <c r="T61" s="288" t="s">
+      <c r="O61" s="121"/>
+      <c r="P61" s="121"/>
+      <c r="Q61" s="121"/>
+      <c r="R61" s="121"/>
+      <c r="S61" s="121"/>
+      <c r="T61" s="33" t="s">
         <v>835</v>
       </c>
-      <c r="U61" s="275"/>
-      <c r="V61" s="336"/>
-      <c r="W61" s="290"/>
-      <c r="X61" s="291"/>
-      <c r="Y61" s="291"/>
-      <c r="Z61" s="291"/>
-      <c r="AA61" s="291"/>
-      <c r="AB61" s="291"/>
-      <c r="AC61" s="340"/>
-      <c r="AD61" s="289"/>
-      <c r="AE61" s="280" t="s">
+      <c r="U61" s="84"/>
+      <c r="V61" s="95"/>
+      <c r="W61" s="289"/>
+      <c r="X61" s="290"/>
+      <c r="Y61" s="290"/>
+      <c r="Z61" s="290"/>
+      <c r="AA61" s="290"/>
+      <c r="AB61" s="290"/>
+      <c r="AC61" s="72"/>
+      <c r="AD61" s="85"/>
+      <c r="AE61" s="73" t="s">
         <v>742</v>
       </c>
-      <c r="AF61" s="280" t="s">
+      <c r="AF61" s="73" t="s">
         <v>828</v>
       </c>
     </row>
@@ -11887,132 +11729,132 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="2" customFormat="1" ht="25.7" customHeight="1">
-      <c r="A1" s="353" t="s">
+      <c r="A1" s="282" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="353"/>
-      <c r="C1" s="353"/>
-      <c r="D1" s="353"/>
-      <c r="E1" s="353"/>
-      <c r="F1" s="353"/>
-      <c r="G1" s="353"/>
-      <c r="H1" s="353"/>
-      <c r="I1" s="353"/>
-      <c r="J1" s="353"/>
-      <c r="K1" s="353"/>
-      <c r="L1" s="353"/>
-      <c r="M1" s="353"/>
-      <c r="N1" s="353"/>
-      <c r="O1" s="353"/>
-      <c r="P1" s="353"/>
-      <c r="Q1" s="353"/>
+      <c r="B1" s="282"/>
+      <c r="C1" s="282"/>
+      <c r="D1" s="282"/>
+      <c r="E1" s="282"/>
+      <c r="F1" s="282"/>
+      <c r="G1" s="282"/>
+      <c r="H1" s="282"/>
+      <c r="I1" s="282"/>
+      <c r="J1" s="282"/>
+      <c r="K1" s="282"/>
+      <c r="L1" s="282"/>
+      <c r="M1" s="282"/>
+      <c r="N1" s="282"/>
+      <c r="O1" s="282"/>
+      <c r="P1" s="282"/>
+      <c r="Q1" s="282"/>
     </row>
     <row r="2" spans="1:18" s="2" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A2" s="353" t="s">
+      <c r="A2" s="282" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="353"/>
-      <c r="C2" s="353"/>
-      <c r="D2" s="353"/>
-      <c r="E2" s="353"/>
-      <c r="F2" s="353"/>
-      <c r="G2" s="353"/>
-      <c r="H2" s="353"/>
-      <c r="I2" s="353"/>
-      <c r="J2" s="353"/>
-      <c r="K2" s="353"/>
-      <c r="L2" s="353"/>
-      <c r="M2" s="353"/>
-      <c r="N2" s="353"/>
-      <c r="O2" s="353"/>
-      <c r="P2" s="353"/>
-      <c r="Q2" s="353"/>
+      <c r="B2" s="282"/>
+      <c r="C2" s="282"/>
+      <c r="D2" s="282"/>
+      <c r="E2" s="282"/>
+      <c r="F2" s="282"/>
+      <c r="G2" s="282"/>
+      <c r="H2" s="282"/>
+      <c r="I2" s="282"/>
+      <c r="J2" s="282"/>
+      <c r="K2" s="282"/>
+      <c r="L2" s="282"/>
+      <c r="M2" s="282"/>
+      <c r="N2" s="282"/>
+      <c r="O2" s="282"/>
+      <c r="P2" s="282"/>
+      <c r="Q2" s="282"/>
     </row>
     <row r="3" spans="1:18" s="3" customFormat="1" ht="37.9" customHeight="1">
-      <c r="A3" s="354" t="s">
+      <c r="A3" s="283" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="355"/>
-      <c r="C3" s="355"/>
-      <c r="D3" s="355" t="s">
+      <c r="B3" s="284"/>
+      <c r="C3" s="284"/>
+      <c r="D3" s="284" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="355"/>
-      <c r="F3" s="355"/>
-      <c r="G3" s="355"/>
-      <c r="H3" s="355"/>
-      <c r="I3" s="355"/>
-      <c r="J3" s="355"/>
-      <c r="K3" s="355"/>
-      <c r="L3" s="355"/>
-      <c r="M3" s="355"/>
-      <c r="N3" s="355"/>
-      <c r="O3" s="355"/>
-      <c r="P3" s="355"/>
-      <c r="Q3" s="356"/>
+      <c r="E3" s="284"/>
+      <c r="F3" s="284"/>
+      <c r="G3" s="284"/>
+      <c r="H3" s="284"/>
+      <c r="I3" s="284"/>
+      <c r="J3" s="284"/>
+      <c r="K3" s="284"/>
+      <c r="L3" s="284"/>
+      <c r="M3" s="284"/>
+      <c r="N3" s="284"/>
+      <c r="O3" s="284"/>
+      <c r="P3" s="284"/>
+      <c r="Q3" s="285"/>
     </row>
     <row r="4" spans="1:18" s="4" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A4" s="343" t="s">
+      <c r="A4" s="272" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="344"/>
-      <c r="C4" s="344"/>
-      <c r="D4" s="344"/>
-      <c r="E4" s="344"/>
-      <c r="F4" s="344"/>
-      <c r="G4" s="344"/>
-      <c r="H4" s="344"/>
-      <c r="I4" s="344"/>
-      <c r="J4" s="344"/>
-      <c r="K4" s="344"/>
-      <c r="L4" s="344"/>
-      <c r="M4" s="344"/>
-      <c r="N4" s="344"/>
-      <c r="O4" s="344"/>
-      <c r="P4" s="344"/>
-      <c r="Q4" s="345"/>
+      <c r="B4" s="273"/>
+      <c r="C4" s="273"/>
+      <c r="D4" s="273"/>
+      <c r="E4" s="273"/>
+      <c r="F4" s="273"/>
+      <c r="G4" s="273"/>
+      <c r="H4" s="273"/>
+      <c r="I4" s="273"/>
+      <c r="J4" s="273"/>
+      <c r="K4" s="273"/>
+      <c r="L4" s="273"/>
+      <c r="M4" s="273"/>
+      <c r="N4" s="273"/>
+      <c r="O4" s="273"/>
+      <c r="P4" s="273"/>
+      <c r="Q4" s="274"/>
     </row>
     <row r="5" spans="1:18" s="5" customFormat="1" ht="49.5">
-      <c r="A5" s="351" t="s">
+      <c r="A5" s="280" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="346" t="s">
+      <c r="B5" s="275" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="346" t="s">
+      <c r="C5" s="275" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="346" t="s">
+      <c r="D5" s="275" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="347"/>
-      <c r="F5" s="347"/>
-      <c r="G5" s="347"/>
-      <c r="H5" s="347"/>
-      <c r="I5" s="347"/>
-      <c r="J5" s="347"/>
-      <c r="K5" s="346" t="s">
+      <c r="E5" s="276"/>
+      <c r="F5" s="276"/>
+      <c r="G5" s="276"/>
+      <c r="H5" s="276"/>
+      <c r="I5" s="276"/>
+      <c r="J5" s="276"/>
+      <c r="K5" s="275" t="s">
         <v>80</v>
       </c>
       <c r="L5" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="M5" s="348" t="s">
+      <c r="M5" s="277" t="s">
         <v>82</v>
       </c>
-      <c r="N5" s="348"/>
-      <c r="O5" s="349"/>
-      <c r="P5" s="352" t="s">
+      <c r="N5" s="277"/>
+      <c r="O5" s="278"/>
+      <c r="P5" s="281" t="s">
         <v>83</v>
       </c>
-      <c r="Q5" s="352" t="s">
+      <c r="Q5" s="281" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:18" s="6" customFormat="1" ht="33" customHeight="1">
-      <c r="A6" s="351"/>
-      <c r="B6" s="346"/>
-      <c r="C6" s="346"/>
+      <c r="A6" s="280"/>
+      <c r="B6" s="275"/>
+      <c r="C6" s="275"/>
       <c r="D6" s="9" t="s">
         <v>84</v>
       </c>
@@ -12034,7 +11876,7 @@
       <c r="J6" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="K6" s="347"/>
+      <c r="K6" s="276"/>
       <c r="L6" s="9" t="s">
         <v>90</v>
       </c>
@@ -12047,8 +11889,8 @@
       <c r="O6" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="P6" s="352"/>
-      <c r="Q6" s="352"/>
+      <c r="P6" s="281"/>
+      <c r="Q6" s="281"/>
     </row>
     <row r="7" spans="1:18" s="7" customFormat="1" ht="37.15" customHeight="1">
       <c r="A7" s="12" t="s">
@@ -12335,15 +12177,15 @@
       <c r="A17" s="12"/>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
-      <c r="D17" s="350" t="s">
+      <c r="D17" s="279" t="s">
         <v>100</v>
       </c>
-      <c r="E17" s="350"/>
-      <c r="F17" s="350"/>
-      <c r="G17" s="350"/>
-      <c r="H17" s="350"/>
-      <c r="I17" s="350"/>
-      <c r="J17" s="350"/>
+      <c r="E17" s="279"/>
+      <c r="F17" s="279"/>
+      <c r="G17" s="279"/>
+      <c r="H17" s="279"/>
+      <c r="I17" s="279"/>
+      <c r="J17" s="279"/>
       <c r="K17" s="12"/>
       <c r="L17" s="14"/>
       <c r="M17" s="14"/>
@@ -14739,10 +14581,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="147" customFormat="1" ht="57.75" customHeight="1">
-      <c r="A1" s="341" t="s">
+      <c r="A1" s="270" t="s">
         <v>785</v>
       </c>
-      <c r="B1" s="342"/>
+      <c r="B1" s="271"/>
       <c r="C1" s="148"/>
       <c r="D1" s="150"/>
       <c r="E1" s="150"/>
